--- a/research/traditional_assets/database/data/hong_kong/hong_kong_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_beverage_soft.xlsx
@@ -1534,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1671,22 +1671,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07946791842877482</v>
+        <v>0.07937437136336734</v>
       </c>
       <c r="C2">
-        <v>915.4067191684912</v>
+        <v>906.418857643243</v>
       </c>
       <c r="D2">
-        <v>411.5067191684912</v>
+        <v>411.673857643243</v>
       </c>
       <c r="E2">
-        <v>-15.2</v>
+        <v>-6.045</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.154999999999999</v>
       </c>
       <c r="G2">
         <v>503.9</v>
@@ -1707,28 +1707,28 @@
         <v>243.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4604964999999999</v>
       </c>
       <c r="N2">
-        <v>243.8</v>
+        <v>243.3395035</v>
       </c>
       <c r="O2">
-        <v>40.227</v>
+        <v>40.15101807750001</v>
       </c>
       <c r="P2">
-        <v>203.573</v>
+        <v>203.1884854225</v>
       </c>
       <c r="Q2">
-        <v>307.773</v>
+        <v>307.3884854225</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07946791842877482</v>
+        <v>0.07975188521552257</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6617854374612541</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>529.4285624320707</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1753,22 +1753,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07937437136336734</v>
+        <v>0.07928082429795985</v>
       </c>
       <c r="C3">
-        <v>906.418857643243</v>
+        <v>897.4311319438239</v>
       </c>
       <c r="D3">
-        <v>411.673857643243</v>
+        <v>411.8411319438238</v>
       </c>
       <c r="E3">
-        <v>-6.045</v>
+        <v>3.109999999999999</v>
       </c>
       <c r="F3">
-        <v>9.154999999999999</v>
+        <v>18.31</v>
       </c>
       <c r="G3">
         <v>503.9</v>
@@ -1789,28 +1789,28 @@
         <v>243.8</v>
       </c>
       <c r="M3">
-        <v>0.4604964999999999</v>
+        <v>0.9209929999999998</v>
       </c>
       <c r="N3">
-        <v>243.3395035</v>
+        <v>242.879007</v>
       </c>
       <c r="O3">
-        <v>40.15101807750001</v>
+        <v>40.075036155</v>
       </c>
       <c r="P3">
-        <v>203.1884854225</v>
+        <v>202.803970845</v>
       </c>
       <c r="Q3">
-        <v>307.3884854225</v>
+        <v>307.003970845</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07975188521552257</v>
+        <v>0.08004164724281618</v>
       </c>
       <c r="T3">
-        <v>0.6617854374612541</v>
+        <v>0.6674334387069845</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>529.4285624320707</v>
+        <v>264.7142812160354</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1835,22 +1835,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07928082429795985</v>
+        <v>0.07918727723255237</v>
       </c>
       <c r="C4">
-        <v>897.4311319438239</v>
+        <v>888.4435422358698</v>
       </c>
       <c r="D4">
-        <v>411.8411319438238</v>
+        <v>412.0085422358698</v>
       </c>
       <c r="E4">
-        <v>3.109999999999999</v>
+        <v>12.265</v>
       </c>
       <c r="F4">
-        <v>18.31</v>
+        <v>27.465</v>
       </c>
       <c r="G4">
         <v>503.9</v>
@@ -1871,28 +1871,28 @@
         <v>243.8</v>
       </c>
       <c r="M4">
-        <v>0.9209929999999998</v>
+        <v>1.3814895</v>
       </c>
       <c r="N4">
-        <v>242.879007</v>
+        <v>242.4185105</v>
       </c>
       <c r="O4">
-        <v>40.075036155</v>
+        <v>39.99905423250001</v>
       </c>
       <c r="P4">
-        <v>202.803970845</v>
+        <v>202.4194562675</v>
       </c>
       <c r="Q4">
-        <v>307.003970845</v>
+        <v>306.6194562675</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08004164724281618</v>
+        <v>0.08033738374489935</v>
       </c>
       <c r="T4">
-        <v>0.6674334387069845</v>
+        <v>0.6731978935866475</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>264.7142812160354</v>
+        <v>176.4761874773569</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1917,22 +1917,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07918727723255237</v>
+        <v>0.07909373016714491</v>
       </c>
       <c r="C5">
-        <v>888.4435422358698</v>
+        <v>879.4560886852872</v>
       </c>
       <c r="D5">
-        <v>412.0085422358698</v>
+        <v>412.1760886852872</v>
       </c>
       <c r="E5">
-        <v>12.265</v>
+        <v>21.42</v>
       </c>
       <c r="F5">
-        <v>27.465</v>
+        <v>36.62</v>
       </c>
       <c r="G5">
         <v>503.9</v>
@@ -1953,28 +1953,28 @@
         <v>243.8</v>
       </c>
       <c r="M5">
-        <v>1.3814895</v>
+        <v>1.841986</v>
       </c>
       <c r="N5">
-        <v>242.4185105</v>
+        <v>241.958014</v>
       </c>
       <c r="O5">
-        <v>39.99905423250001</v>
+        <v>39.92307231</v>
       </c>
       <c r="P5">
-        <v>202.4194562675</v>
+        <v>202.03494169</v>
       </c>
       <c r="Q5">
-        <v>306.6194562675</v>
+        <v>306.23494169</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08033738374489935</v>
+        <v>0.08063928142410928</v>
       </c>
       <c r="T5">
-        <v>0.6731978935866475</v>
+        <v>0.6790824412763036</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>176.4761874773569</v>
+        <v>132.3571406080177</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1999,22 +1999,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07909373016714491</v>
+        <v>0.07900018310173743</v>
       </c>
       <c r="C6">
-        <v>879.4560886852872</v>
+        <v>870.4687714582517</v>
       </c>
       <c r="D6">
-        <v>412.1760886852872</v>
+        <v>412.3437714582517</v>
       </c>
       <c r="E6">
-        <v>21.42</v>
+        <v>30.57500000000001</v>
       </c>
       <c r="F6">
-        <v>36.62</v>
+        <v>45.77500000000001</v>
       </c>
       <c r="G6">
         <v>503.9</v>
@@ -2035,28 +2035,28 @@
         <v>243.8</v>
       </c>
       <c r="M6">
-        <v>1.841986</v>
+        <v>2.3024825</v>
       </c>
       <c r="N6">
-        <v>241.958014</v>
+        <v>241.4975175</v>
       </c>
       <c r="O6">
-        <v>39.92307231</v>
+        <v>39.8470903875</v>
       </c>
       <c r="P6">
-        <v>202.03494169</v>
+        <v>201.6504271125</v>
       </c>
       <c r="Q6">
-        <v>306.23494169</v>
+        <v>305.8504271125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08063928142410928</v>
+        <v>0.08094753484393413</v>
       </c>
       <c r="T6">
-        <v>0.6790824412763036</v>
+        <v>0.6850908741804786</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>132.3571406080177</v>
+        <v>105.8857124864141</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07900018310173743</v>
+        <v>0.07890663603632996</v>
       </c>
       <c r="C7">
-        <v>870.4687714582517</v>
+        <v>861.4815907212098</v>
       </c>
       <c r="D7">
-        <v>412.3437714582517</v>
+        <v>412.5115907212098</v>
       </c>
       <c r="E7">
-        <v>30.57500000000001</v>
+        <v>39.73</v>
       </c>
       <c r="F7">
-        <v>45.77500000000001</v>
+        <v>54.93000000000001</v>
       </c>
       <c r="G7">
         <v>503.9</v>
@@ -2117,28 +2117,28 @@
         <v>243.8</v>
       </c>
       <c r="M7">
-        <v>2.3024825</v>
+        <v>2.762979</v>
       </c>
       <c r="N7">
-        <v>241.4975175</v>
+        <v>241.037021</v>
       </c>
       <c r="O7">
-        <v>39.8470903875</v>
+        <v>39.771108465</v>
       </c>
       <c r="P7">
-        <v>201.6504271125</v>
+        <v>201.265912535</v>
       </c>
       <c r="Q7">
-        <v>305.8504271125</v>
+        <v>305.465912535</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08094753484393413</v>
+        <v>0.08126234684715952</v>
       </c>
       <c r="T7">
-        <v>0.6850908741804786</v>
+        <v>0.6912271460826148</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>105.8857124864141</v>
+        <v>88.23809373867843</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2163,22 +2163,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07890663603632994</v>
+        <v>0.07881308897092247</v>
       </c>
       <c r="C8">
-        <v>861.48159072121</v>
+        <v>852.4945466408792</v>
       </c>
       <c r="D8">
-        <v>412.5115907212099</v>
+        <v>412.6795466408793</v>
       </c>
       <c r="E8">
-        <v>39.73</v>
+        <v>48.88499999999999</v>
       </c>
       <c r="F8">
-        <v>54.93</v>
+        <v>64.08499999999999</v>
       </c>
       <c r="G8">
         <v>503.9</v>
@@ -2199,28 +2199,28 @@
         <v>243.8</v>
       </c>
       <c r="M8">
-        <v>2.762979</v>
+        <v>3.2234755</v>
       </c>
       <c r="N8">
-        <v>241.037021</v>
+        <v>240.5765245</v>
       </c>
       <c r="O8">
-        <v>39.771108465</v>
+        <v>39.69512654250001</v>
       </c>
       <c r="P8">
-        <v>201.265912535</v>
+        <v>200.8813979575</v>
       </c>
       <c r="Q8">
-        <v>305.465912535</v>
+        <v>305.0813979575</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08126234684715952</v>
+        <v>0.0815839290009919</v>
       </c>
       <c r="T8">
-        <v>0.6912271460826148</v>
+        <v>0.6974953808213561</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>88.23809373867844</v>
+        <v>75.63265177601009</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2245,22 +2245,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07881308897092246</v>
+        <v>0.07871954190551499</v>
       </c>
       <c r="C9">
-        <v>852.4945466408792</v>
+        <v>843.5076393842488</v>
       </c>
       <c r="D9">
-        <v>412.6795466408793</v>
+        <v>412.8476393842489</v>
       </c>
       <c r="E9">
-        <v>48.88500000000001</v>
+        <v>58.03999999999999</v>
       </c>
       <c r="F9">
-        <v>64.08500000000001</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="G9">
         <v>503.9</v>
@@ -2281,28 +2281,28 @@
         <v>243.8</v>
       </c>
       <c r="M9">
-        <v>3.2234755</v>
+        <v>3.683971999999999</v>
       </c>
       <c r="N9">
-        <v>240.5765245</v>
+        <v>240.116028</v>
       </c>
       <c r="O9">
-        <v>39.69512654250001</v>
+        <v>39.61914462</v>
       </c>
       <c r="P9">
-        <v>200.8813979575</v>
+        <v>200.49688338</v>
       </c>
       <c r="Q9">
-        <v>305.0813979575</v>
+        <v>304.69688338</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0815839290009919</v>
+        <v>0.08191250207121194</v>
       </c>
       <c r="T9">
-        <v>0.6974953808213562</v>
+        <v>0.7038998815326787</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>75.63265177601008</v>
+        <v>66.17857030400884</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2327,22 +2327,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07871954190551499</v>
+        <v>0.0786259948401075</v>
       </c>
       <c r="C10">
-        <v>843.5076393842488</v>
+        <v>834.52086911858</v>
       </c>
       <c r="D10">
-        <v>412.8476393842489</v>
+        <v>413.01586911858</v>
       </c>
       <c r="E10">
-        <v>58.03999999999999</v>
+        <v>67.19499999999999</v>
       </c>
       <c r="F10">
-        <v>73.23999999999999</v>
+        <v>82.395</v>
       </c>
       <c r="G10">
         <v>503.9</v>
@@ -2363,28 +2363,28 @@
         <v>243.8</v>
       </c>
       <c r="M10">
-        <v>3.683971999999999</v>
+        <v>4.144468499999999</v>
       </c>
       <c r="N10">
-        <v>240.116028</v>
+        <v>239.6555315</v>
       </c>
       <c r="O10">
-        <v>39.61914462</v>
+        <v>39.54316269750001</v>
       </c>
       <c r="P10">
-        <v>200.49688338</v>
+        <v>200.1123688025</v>
       </c>
       <c r="Q10">
-        <v>304.69688338</v>
+        <v>304.3123688025</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08191250207121194</v>
+        <v>0.08224829652759066</v>
       </c>
       <c r="T10">
-        <v>0.7038998815326787</v>
+        <v>0.7104451405013931</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>66.17857030400884</v>
+        <v>58.82539582578563</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0786259948401075</v>
+        <v>0.07853244777470003</v>
       </c>
       <c r="C11">
-        <v>834.52086911858</v>
+        <v>825.534236011407</v>
       </c>
       <c r="D11">
-        <v>413.01586911858</v>
+        <v>413.1842360114069</v>
       </c>
       <c r="E11">
-        <v>67.19499999999999</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="F11">
-        <v>82.395</v>
+        <v>91.55</v>
       </c>
       <c r="G11">
         <v>503.9</v>
@@ -2445,28 +2445,28 @@
         <v>243.8</v>
       </c>
       <c r="M11">
-        <v>4.144468499999999</v>
+        <v>4.604965</v>
       </c>
       <c r="N11">
-        <v>239.6555315</v>
+        <v>239.195035</v>
       </c>
       <c r="O11">
-        <v>39.54316269750001</v>
+        <v>39.467180775</v>
       </c>
       <c r="P11">
-        <v>200.1123688025</v>
+        <v>199.727854225</v>
       </c>
       <c r="Q11">
-        <v>304.3123688025</v>
+        <v>303.927854225</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08224829652759066</v>
+        <v>0.08259155308300004</v>
       </c>
       <c r="T11">
-        <v>0.7104451405013931</v>
+        <v>0.7171358496694122</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>58.82539582578563</v>
+        <v>52.94285624320707</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2491,22 +2491,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07853244777470003</v>
+        <v>0.07843890070929255</v>
       </c>
       <c r="C12">
-        <v>825.5342360114068</v>
+        <v>816.5477402305368</v>
       </c>
       <c r="D12">
-        <v>413.1842360114069</v>
+        <v>413.3527402305369</v>
       </c>
       <c r="E12">
-        <v>76.35000000000001</v>
+        <v>85.505</v>
       </c>
       <c r="F12">
-        <v>91.55000000000001</v>
+        <v>100.705</v>
       </c>
       <c r="G12">
         <v>503.9</v>
@@ -2527,28 +2527,28 @@
         <v>243.8</v>
       </c>
       <c r="M12">
-        <v>4.604965</v>
+        <v>5.0654615</v>
       </c>
       <c r="N12">
-        <v>239.195035</v>
+        <v>238.7345385</v>
       </c>
       <c r="O12">
-        <v>39.467180775</v>
+        <v>39.3911988525</v>
       </c>
       <c r="P12">
-        <v>199.727854225</v>
+        <v>199.3433396475</v>
       </c>
       <c r="Q12">
-        <v>303.927854225</v>
+        <v>303.5433396475</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08259155308300004</v>
+        <v>0.08294252326886803</v>
       </c>
       <c r="T12">
-        <v>0.7171358496694122</v>
+        <v>0.7239769118524431</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>52.94285624320707</v>
+        <v>48.12986931200643</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2573,22 +2573,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07843890070929255</v>
+        <v>0.07834535364388508</v>
       </c>
       <c r="C13">
-        <v>816.5477402305368</v>
+        <v>807.561381944051</v>
       </c>
       <c r="D13">
-        <v>413.3527402305369</v>
+        <v>413.521381944051</v>
       </c>
       <c r="E13">
-        <v>85.505</v>
+        <v>94.66</v>
       </c>
       <c r="F13">
-        <v>100.705</v>
+        <v>109.86</v>
       </c>
       <c r="G13">
         <v>503.9</v>
@@ -2609,28 +2609,28 @@
         <v>243.8</v>
       </c>
       <c r="M13">
-        <v>5.0654615</v>
+        <v>5.525957999999999</v>
       </c>
       <c r="N13">
-        <v>238.7345385</v>
+        <v>238.274042</v>
       </c>
       <c r="O13">
-        <v>39.3911988525</v>
+        <v>39.31521693000001</v>
       </c>
       <c r="P13">
-        <v>199.3433396475</v>
+        <v>198.95882507</v>
       </c>
       <c r="Q13">
-        <v>303.5433396475</v>
+        <v>303.15882507</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08294252326886803</v>
+        <v>0.0833014700498694</v>
       </c>
       <c r="T13">
-        <v>0.7239769118524431</v>
+        <v>0.7309734527214518</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>48.12986931200643</v>
+        <v>44.11904686933922</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2655,22 +2655,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07834535364388508</v>
+        <v>0.07825180657847759</v>
       </c>
       <c r="C14">
-        <v>807.561381944051</v>
+        <v>798.5751613203051</v>
       </c>
       <c r="D14">
-        <v>413.521381944051</v>
+        <v>413.6901613203052</v>
       </c>
       <c r="E14">
-        <v>94.66</v>
+        <v>103.815</v>
       </c>
       <c r="F14">
-        <v>109.86</v>
+        <v>119.015</v>
       </c>
       <c r="G14">
         <v>503.9</v>
@@ -2691,28 +2691,28 @@
         <v>243.8</v>
       </c>
       <c r="M14">
-        <v>5.525957999999999</v>
+        <v>5.9864545</v>
       </c>
       <c r="N14">
-        <v>238.274042</v>
+        <v>237.8135455</v>
       </c>
       <c r="O14">
-        <v>39.31521693000001</v>
+        <v>39.2392350075</v>
       </c>
       <c r="P14">
-        <v>198.95882507</v>
+        <v>198.5743104925</v>
       </c>
       <c r="Q14">
-        <v>303.15882507</v>
+        <v>302.7743104925</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0833014700498694</v>
+        <v>0.08366866848100873</v>
       </c>
       <c r="T14">
-        <v>0.7309734527214518</v>
+        <v>0.7381308336104377</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>44.11904686933922</v>
+        <v>40.7252740332362</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2737,22 +2737,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07825180657847759</v>
+        <v>0.07815825951307011</v>
       </c>
       <c r="C15">
-        <v>798.5751613203051</v>
+        <v>789.5890785279296</v>
       </c>
       <c r="D15">
-        <v>413.6901613203052</v>
+        <v>413.8590785279296</v>
       </c>
       <c r="E15">
-        <v>103.815</v>
+        <v>112.97</v>
       </c>
       <c r="F15">
-        <v>119.015</v>
+        <v>128.17</v>
       </c>
       <c r="G15">
         <v>503.9</v>
@@ -2773,28 +2773,28 @@
         <v>243.8</v>
       </c>
       <c r="M15">
-        <v>5.9864545</v>
+        <v>6.446951</v>
       </c>
       <c r="N15">
-        <v>237.8135455</v>
+        <v>237.353049</v>
       </c>
       <c r="O15">
-        <v>39.2392350075</v>
+        <v>39.163253085</v>
       </c>
       <c r="P15">
-        <v>198.5743104925</v>
+        <v>198.189795915</v>
       </c>
       <c r="Q15">
-        <v>302.7743104925</v>
+        <v>302.389795915</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08366866848100873</v>
+        <v>0.08404440641054664</v>
       </c>
       <c r="T15">
-        <v>0.7381308336104377</v>
+        <v>0.7454546652177723</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>40.7252740332362</v>
+        <v>37.81632588800504</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2819,22 +2819,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07815825951307011</v>
+        <v>0.07806471244766264</v>
       </c>
       <c r="C16">
-        <v>789.5890785279296</v>
+        <v>780.6031337358307</v>
       </c>
       <c r="D16">
-        <v>413.8590785279296</v>
+        <v>414.0281337358308</v>
       </c>
       <c r="E16">
-        <v>112.97</v>
+        <v>122.125</v>
       </c>
       <c r="F16">
-        <v>128.17</v>
+        <v>137.325</v>
       </c>
       <c r="G16">
         <v>503.9</v>
@@ -2855,28 +2855,28 @@
         <v>243.8</v>
       </c>
       <c r="M16">
-        <v>6.446951</v>
+        <v>6.907447500000001</v>
       </c>
       <c r="N16">
-        <v>237.353049</v>
+        <v>236.8925525</v>
       </c>
       <c r="O16">
-        <v>39.163253085</v>
+        <v>39.0872711625</v>
       </c>
       <c r="P16">
-        <v>198.189795915</v>
+        <v>197.8052813375</v>
       </c>
       <c r="Q16">
-        <v>302.389795915</v>
+        <v>302.0052813375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08404440641054664</v>
+        <v>0.08442898523254427</v>
       </c>
       <c r="T16">
-        <v>0.7454546652177723</v>
+        <v>0.7529508222746911</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>37.81632588800504</v>
+        <v>35.29523749547137</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2901,22 +2901,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07806471244766264</v>
+        <v>0.07797116538225517</v>
       </c>
       <c r="C17">
-        <v>780.6031337358309</v>
+        <v>771.6173271131906</v>
       </c>
       <c r="D17">
-        <v>414.0281337358308</v>
+        <v>414.1973271131907</v>
       </c>
       <c r="E17">
-        <v>122.125</v>
+        <v>131.28</v>
       </c>
       <c r="F17">
-        <v>137.325</v>
+        <v>146.48</v>
       </c>
       <c r="G17">
         <v>503.9</v>
@@ -2937,28 +2937,28 @@
         <v>243.8</v>
       </c>
       <c r="M17">
-        <v>6.907447499999999</v>
+        <v>7.367943999999999</v>
       </c>
       <c r="N17">
-        <v>236.8925525</v>
+        <v>236.432056</v>
       </c>
       <c r="O17">
-        <v>39.0872711625</v>
+        <v>39.01128924</v>
       </c>
       <c r="P17">
-        <v>197.8052813375</v>
+        <v>197.42076676</v>
       </c>
       <c r="Q17">
-        <v>302.0052813375</v>
+        <v>301.62076676</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08442898523254427</v>
+        <v>0.08482272069316091</v>
       </c>
       <c r="T17">
-        <v>0.7529508222746911</v>
+        <v>0.7606254592615366</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>35.29523749547138</v>
+        <v>33.08928515200442</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2983,22 +2983,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07797116538225517</v>
+        <v>0.07787761831684768</v>
       </c>
       <c r="C18">
-        <v>771.6173271131906</v>
+        <v>762.6316588294683</v>
       </c>
       <c r="D18">
-        <v>414.1973271131907</v>
+        <v>414.3666588294683</v>
       </c>
       <c r="E18">
-        <v>131.28</v>
+        <v>140.435</v>
       </c>
       <c r="F18">
-        <v>146.48</v>
+        <v>155.635</v>
       </c>
       <c r="G18">
         <v>503.9</v>
@@ -3019,28 +3019,28 @@
         <v>243.8</v>
       </c>
       <c r="M18">
-        <v>7.367943999999999</v>
+        <v>7.828440500000001</v>
       </c>
       <c r="N18">
-        <v>236.432056</v>
+        <v>235.9715595</v>
       </c>
       <c r="O18">
-        <v>39.01128924</v>
+        <v>38.9353073175</v>
       </c>
       <c r="P18">
-        <v>197.42076676</v>
+        <v>197.0362521825</v>
       </c>
       <c r="Q18">
-        <v>301.62076676</v>
+        <v>301.2362521825</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08482272069316091</v>
+        <v>0.08522594375523818</v>
       </c>
       <c r="T18">
-        <v>0.7606254592615366</v>
+        <v>0.7684850272601133</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>33.08928515200442</v>
+        <v>31.14285661365121</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3065,22 +3065,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07787761831684768</v>
+        <v>0.07778407125144021</v>
       </c>
       <c r="C19">
-        <v>762.6316588294683</v>
+        <v>753.6461290543998</v>
       </c>
       <c r="D19">
-        <v>414.3666588294683</v>
+        <v>414.5361290543997</v>
       </c>
       <c r="E19">
-        <v>140.435</v>
+        <v>149.59</v>
       </c>
       <c r="F19">
-        <v>155.635</v>
+        <v>164.79</v>
       </c>
       <c r="G19">
         <v>503.9</v>
@@ -3101,28 +3101,28 @@
         <v>243.8</v>
       </c>
       <c r="M19">
-        <v>7.828440500000001</v>
+        <v>8.288937000000001</v>
       </c>
       <c r="N19">
-        <v>235.9715595</v>
+        <v>235.511063</v>
       </c>
       <c r="O19">
-        <v>38.9353073175</v>
+        <v>38.85932539500001</v>
       </c>
       <c r="P19">
-        <v>197.0362521825</v>
+        <v>196.651737605</v>
       </c>
       <c r="Q19">
-        <v>301.2362521825</v>
+        <v>300.851737605</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08522594375523818</v>
+        <v>0.08563900152614659</v>
       </c>
       <c r="T19">
-        <v>0.7684850272601133</v>
+        <v>0.776536292039143</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>31.14285661365121</v>
+        <v>29.41269791289281</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07778407125144021</v>
+        <v>0.07769052418603273</v>
       </c>
       <c r="C20">
-        <v>753.6461290543998</v>
+        <v>744.6607379579989</v>
       </c>
       <c r="D20">
-        <v>414.5361290543997</v>
+        <v>414.7057379579988</v>
       </c>
       <c r="E20">
-        <v>149.59</v>
+        <v>158.745</v>
       </c>
       <c r="F20">
-        <v>164.79</v>
+        <v>173.945</v>
       </c>
       <c r="G20">
         <v>503.9</v>
@@ -3183,28 +3183,28 @@
         <v>243.8</v>
       </c>
       <c r="M20">
-        <v>8.288936999999999</v>
+        <v>8.749433499999999</v>
       </c>
       <c r="N20">
-        <v>235.511063</v>
+        <v>235.0505665</v>
       </c>
       <c r="O20">
-        <v>38.85932539500001</v>
+        <v>38.7833434725</v>
       </c>
       <c r="P20">
-        <v>196.651737605</v>
+        <v>196.2672230275</v>
       </c>
       <c r="Q20">
-        <v>300.851737605</v>
+        <v>300.4672230275</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08563900152614659</v>
+        <v>0.08606225825436138</v>
       </c>
       <c r="T20">
-        <v>0.776536292039143</v>
+        <v>0.7847863534793833</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>29.41269791289282</v>
+        <v>27.8646611806353</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3229,22 +3229,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07769052418603273</v>
+        <v>0.07759697712062523</v>
       </c>
       <c r="C21">
-        <v>744.6607379579989</v>
+        <v>735.6754857105578</v>
       </c>
       <c r="D21">
-        <v>414.7057379579988</v>
+        <v>414.8754857105579</v>
       </c>
       <c r="E21">
-        <v>158.745</v>
+        <v>167.9</v>
       </c>
       <c r="F21">
-        <v>173.945</v>
+        <v>183.1</v>
       </c>
       <c r="G21">
         <v>503.9</v>
@@ -3265,28 +3265,28 @@
         <v>243.8</v>
       </c>
       <c r="M21">
-        <v>8.749433499999999</v>
+        <v>9.20993</v>
       </c>
       <c r="N21">
-        <v>235.0505665</v>
+        <v>234.59007</v>
       </c>
       <c r="O21">
-        <v>38.7833434725</v>
+        <v>38.70736155000001</v>
       </c>
       <c r="P21">
-        <v>196.2672230275</v>
+        <v>195.88270845</v>
       </c>
       <c r="Q21">
-        <v>300.4672230275</v>
+        <v>300.08270845</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08606225825436138</v>
+        <v>0.08649609640078154</v>
       </c>
       <c r="T21">
-        <v>0.7847863534793833</v>
+        <v>0.7932426664556297</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>27.8646611806353</v>
+        <v>26.47142812160353</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3311,22 +3311,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07759697712062523</v>
+        <v>0.07750343005521776</v>
       </c>
       <c r="C22">
-        <v>735.6754857105578</v>
+        <v>726.6903724826481</v>
       </c>
       <c r="D22">
-        <v>414.8754857105579</v>
+        <v>415.0453724826481</v>
       </c>
       <c r="E22">
-        <v>167.9</v>
+        <v>177.055</v>
       </c>
       <c r="F22">
-        <v>183.1</v>
+        <v>192.255</v>
       </c>
       <c r="G22">
         <v>503.9</v>
@@ -3347,28 +3347,28 @@
         <v>243.8</v>
       </c>
       <c r="M22">
-        <v>9.20993</v>
+        <v>9.670426500000001</v>
       </c>
       <c r="N22">
-        <v>234.59007</v>
+        <v>234.1295735</v>
       </c>
       <c r="O22">
-        <v>38.70736155000001</v>
+        <v>38.6313796275</v>
       </c>
       <c r="P22">
-        <v>195.88270845</v>
+        <v>195.4981938725</v>
       </c>
       <c r="Q22">
-        <v>300.08270845</v>
+        <v>299.6981938725</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08649609640078154</v>
+        <v>0.08694091779141488</v>
       </c>
       <c r="T22">
-        <v>0.7932426664556297</v>
+        <v>0.8019130633046924</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>26.47142812160353</v>
+        <v>25.2108839253367</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3393,22 +3393,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07750343005521776</v>
+        <v>0.07740988298981029</v>
       </c>
       <c r="C23">
-        <v>726.6903724826481</v>
+        <v>717.7053984451201</v>
       </c>
       <c r="D23">
-        <v>415.0453724826481</v>
+        <v>415.2153984451201</v>
       </c>
       <c r="E23">
-        <v>177.055</v>
+        <v>186.21</v>
       </c>
       <c r="F23">
-        <v>192.255</v>
+        <v>201.41</v>
       </c>
       <c r="G23">
         <v>503.9</v>
@@ -3429,28 +3429,28 @@
         <v>243.8</v>
       </c>
       <c r="M23">
-        <v>9.6704265</v>
+        <v>10.130923</v>
       </c>
       <c r="N23">
-        <v>234.1295735</v>
+        <v>233.669077</v>
       </c>
       <c r="O23">
-        <v>38.6313796275</v>
+        <v>38.555397705</v>
       </c>
       <c r="P23">
-        <v>195.4981938725</v>
+        <v>195.113679295</v>
       </c>
       <c r="Q23">
-        <v>299.6981938725</v>
+        <v>299.313679295</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08694091779141488</v>
+        <v>0.08739714485873114</v>
       </c>
       <c r="T23">
-        <v>0.8019130633046924</v>
+        <v>0.81080577802168</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>25.2108839253367</v>
+        <v>24.06493465600321</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3475,22 +3475,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07740988298981029</v>
+        <v>0.07731633592440279</v>
       </c>
       <c r="C24">
-        <v>717.7053984451201</v>
+        <v>708.7205637691047</v>
       </c>
       <c r="D24">
-        <v>415.2153984451201</v>
+        <v>415.3855637691048</v>
       </c>
       <c r="E24">
-        <v>186.21</v>
+        <v>195.365</v>
       </c>
       <c r="F24">
-        <v>201.41</v>
+        <v>210.565</v>
       </c>
       <c r="G24">
         <v>503.9</v>
@@ -3511,28 +3511,28 @@
         <v>243.8</v>
       </c>
       <c r="M24">
-        <v>10.130923</v>
+        <v>10.5914195</v>
       </c>
       <c r="N24">
-        <v>233.669077</v>
+        <v>233.2085805</v>
       </c>
       <c r="O24">
-        <v>38.555397705</v>
+        <v>38.47941578250001</v>
       </c>
       <c r="P24">
-        <v>195.113679295</v>
+        <v>194.7291647175</v>
       </c>
       <c r="Q24">
-        <v>299.313679295</v>
+        <v>298.9291647175</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08739714485873114</v>
+        <v>0.08786522197974389</v>
       </c>
       <c r="T24">
-        <v>0.81080577802168</v>
+        <v>0.8199294723417059</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>24.06493465600321</v>
+        <v>23.01863314922046</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3557,22 +3557,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07731633592440279</v>
+        <v>0.07722278885899533</v>
       </c>
       <c r="C25">
-        <v>708.7205637691047</v>
+        <v>699.7358686260133</v>
       </c>
       <c r="D25">
-        <v>415.3855637691048</v>
+        <v>415.5558686260133</v>
       </c>
       <c r="E25">
-        <v>195.365</v>
+        <v>204.52</v>
       </c>
       <c r="F25">
-        <v>210.565</v>
+        <v>219.72</v>
       </c>
       <c r="G25">
         <v>503.9</v>
@@ -3593,28 +3593,28 @@
         <v>243.8</v>
       </c>
       <c r="M25">
-        <v>10.5914195</v>
+        <v>11.051916</v>
       </c>
       <c r="N25">
-        <v>233.2085805</v>
+        <v>232.748084</v>
       </c>
       <c r="O25">
-        <v>38.47941578250001</v>
+        <v>38.40343386</v>
       </c>
       <c r="P25">
-        <v>194.7291647175</v>
+        <v>194.34465014</v>
       </c>
       <c r="Q25">
-        <v>298.9291647175</v>
+        <v>298.54465014</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08786522197974389</v>
+        <v>0.0883456169197307</v>
       </c>
       <c r="T25">
-        <v>0.8199294723417059</v>
+        <v>0.82929326388068</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>23.01863314922046</v>
+        <v>22.05952343466961</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3639,22 +3639,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07722278885899533</v>
+        <v>0.07712924179358785</v>
       </c>
       <c r="C26">
-        <v>699.7358686260133</v>
+        <v>690.7513131875387</v>
       </c>
       <c r="D26">
-        <v>415.5558686260133</v>
+        <v>415.7263131875387</v>
       </c>
       <c r="E26">
-        <v>204.52</v>
+        <v>213.675</v>
       </c>
       <c r="F26">
-        <v>219.72</v>
+        <v>228.875</v>
       </c>
       <c r="G26">
         <v>503.9</v>
@@ -3675,28 +3675,28 @@
         <v>243.8</v>
       </c>
       <c r="M26">
-        <v>11.051916</v>
+        <v>11.5124125</v>
       </c>
       <c r="N26">
-        <v>232.748084</v>
+        <v>232.2875875</v>
       </c>
       <c r="O26">
-        <v>38.40343386</v>
+        <v>38.3274519375</v>
       </c>
       <c r="P26">
-        <v>194.34465014</v>
+        <v>193.9601355625</v>
       </c>
       <c r="Q26">
-        <v>298.54465014</v>
+        <v>298.1601355625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0883456169197307</v>
+        <v>0.08883882239145047</v>
       </c>
       <c r="T26">
-        <v>0.82929326388068</v>
+        <v>0.8389067565273602</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>22.05952343466961</v>
+        <v>21.17714249728282</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3721,22 +3721,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07712924179358785</v>
+        <v>0.07703569472818037</v>
       </c>
       <c r="C27">
-        <v>690.7513131875387</v>
+        <v>681.766897625655</v>
       </c>
       <c r="D27">
-        <v>415.7263131875387</v>
+        <v>415.896897625655</v>
       </c>
       <c r="E27">
-        <v>213.675</v>
+        <v>222.83</v>
       </c>
       <c r="F27">
-        <v>228.875</v>
+        <v>238.03</v>
       </c>
       <c r="G27">
         <v>503.9</v>
@@ -3757,28 +3757,28 @@
         <v>243.8</v>
       </c>
       <c r="M27">
-        <v>11.5124125</v>
+        <v>11.972909</v>
       </c>
       <c r="N27">
-        <v>232.2875875</v>
+        <v>231.827091</v>
       </c>
       <c r="O27">
-        <v>38.3274519375</v>
+        <v>38.251470015</v>
       </c>
       <c r="P27">
-        <v>193.9601355625</v>
+        <v>193.575620985</v>
       </c>
       <c r="Q27">
-        <v>298.1601355625</v>
+        <v>297.775620985</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08883882239145047</v>
+        <v>0.08934535774078428</v>
       </c>
       <c r="T27">
-        <v>0.8389067565273602</v>
+        <v>0.8487800732996262</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>21.17714249728282</v>
+        <v>20.3626370166181</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3803,22 +3803,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07703569472818037</v>
+        <v>0.07694214766277289</v>
       </c>
       <c r="C28">
-        <v>681.766897625655</v>
+        <v>672.7826221126193</v>
       </c>
       <c r="D28">
-        <v>415.896897625655</v>
+        <v>416.0676221126193</v>
       </c>
       <c r="E28">
-        <v>222.83</v>
+        <v>231.985</v>
       </c>
       <c r="F28">
-        <v>238.03</v>
+        <v>247.185</v>
       </c>
       <c r="G28">
         <v>503.9</v>
@@ -3839,28 +3839,28 @@
         <v>243.8</v>
       </c>
       <c r="M28">
-        <v>11.972909</v>
+        <v>12.4334055</v>
       </c>
       <c r="N28">
-        <v>231.827091</v>
+        <v>231.3665945</v>
       </c>
       <c r="O28">
-        <v>38.251470015</v>
+        <v>38.1754880925</v>
       </c>
       <c r="P28">
-        <v>193.575620985</v>
+        <v>193.1911064075</v>
       </c>
       <c r="Q28">
-        <v>297.775620985</v>
+        <v>297.3911064075</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08934535774078428</v>
+        <v>0.08986577077092177</v>
       </c>
       <c r="T28">
-        <v>0.8487800732996262</v>
+        <v>0.8589238919012694</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>20.3626370166181</v>
+        <v>19.60846527526188</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3885,22 +3885,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07694214766277289</v>
+        <v>0.07684860059736541</v>
       </c>
       <c r="C29">
-        <v>672.7826221126193</v>
+        <v>663.7984868209711</v>
       </c>
       <c r="D29">
-        <v>416.0676221126193</v>
+        <v>416.2384868209712</v>
       </c>
       <c r="E29">
-        <v>231.985</v>
+        <v>241.14</v>
       </c>
       <c r="F29">
-        <v>247.185</v>
+        <v>256.34</v>
       </c>
       <c r="G29">
         <v>503.9</v>
@@ -3921,28 +3921,28 @@
         <v>243.8</v>
       </c>
       <c r="M29">
-        <v>12.4334055</v>
+        <v>12.893902</v>
       </c>
       <c r="N29">
-        <v>231.3665945</v>
+        <v>230.906098</v>
       </c>
       <c r="O29">
-        <v>38.1754880925</v>
+        <v>38.09950617000001</v>
       </c>
       <c r="P29">
-        <v>193.1911064075</v>
+        <v>192.80659183</v>
       </c>
       <c r="Q29">
-        <v>297.3911064075</v>
+        <v>297.00659183</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08986577077092177</v>
+        <v>0.09040063971856308</v>
       </c>
       <c r="T29">
-        <v>0.8589238919012694</v>
+        <v>0.8693494832418474</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>19.60846527526188</v>
+        <v>18.90816294400252</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3967,22 +3967,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07684860059736541</v>
+        <v>0.07675505353195794</v>
       </c>
       <c r="C30">
-        <v>663.7984868209711</v>
+        <v>654.8144919235342</v>
       </c>
       <c r="D30">
-        <v>416.2384868209712</v>
+        <v>416.4094919235342</v>
       </c>
       <c r="E30">
-        <v>241.14</v>
+        <v>250.295</v>
       </c>
       <c r="F30">
-        <v>256.34</v>
+        <v>265.495</v>
       </c>
       <c r="G30">
         <v>503.9</v>
@@ -4003,28 +4003,28 @@
         <v>243.8</v>
       </c>
       <c r="M30">
-        <v>12.893902</v>
+        <v>13.3543985</v>
       </c>
       <c r="N30">
-        <v>230.906098</v>
+        <v>230.4456015</v>
       </c>
       <c r="O30">
-        <v>38.09950617000001</v>
+        <v>38.02352424750001</v>
       </c>
       <c r="P30">
-        <v>192.80659183</v>
+        <v>192.4220772525</v>
       </c>
       <c r="Q30">
-        <v>297.00659183</v>
+        <v>296.6220772525</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09040063971856308</v>
+        <v>0.09095057539712387</v>
       </c>
       <c r="T30">
-        <v>0.8693494832418474</v>
+        <v>0.8800687532117371</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>18.90816294400252</v>
+        <v>18.25615732524382</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4049,22 +4049,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07675505353195794</v>
+        <v>0.07666150646655046</v>
       </c>
       <c r="C31">
-        <v>654.8144919235342</v>
+        <v>645.8306375934156</v>
       </c>
       <c r="D31">
-        <v>416.4094919235342</v>
+        <v>416.5806375934157</v>
       </c>
       <c r="E31">
-        <v>250.295</v>
+        <v>259.45</v>
       </c>
       <c r="F31">
-        <v>265.495</v>
+        <v>274.65</v>
       </c>
       <c r="G31">
         <v>503.9</v>
@@ -4085,28 +4085,28 @@
         <v>243.8</v>
       </c>
       <c r="M31">
-        <v>13.3543985</v>
+        <v>13.814895</v>
       </c>
       <c r="N31">
-        <v>230.4456015</v>
+        <v>229.985105</v>
       </c>
       <c r="O31">
-        <v>38.02352424750001</v>
+        <v>37.947542325</v>
       </c>
       <c r="P31">
-        <v>192.4220772525</v>
+        <v>192.037562675</v>
       </c>
       <c r="Q31">
-        <v>296.6220772525</v>
+        <v>296.237562675</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09095057539712387</v>
+        <v>0.09151622352364351</v>
       </c>
       <c r="T31">
-        <v>0.8800687532117371</v>
+        <v>0.8910942880379094</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>18.25615732524382</v>
+        <v>17.64761874773569</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07666150646655046</v>
+        <v>0.07656795940114297</v>
       </c>
       <c r="C32">
-        <v>645.8306375934156</v>
+        <v>636.8469240040076</v>
       </c>
       <c r="D32">
-        <v>416.5806375934157</v>
+        <v>416.7519240040078</v>
       </c>
       <c r="E32">
-        <v>259.45</v>
+        <v>268.605</v>
       </c>
       <c r="F32">
-        <v>274.65</v>
+        <v>283.805</v>
       </c>
       <c r="G32">
         <v>503.9</v>
@@ -4167,28 +4167,28 @@
         <v>243.8</v>
       </c>
       <c r="M32">
-        <v>13.814895</v>
+        <v>14.2753915</v>
       </c>
       <c r="N32">
-        <v>229.985105</v>
+        <v>229.5246085</v>
       </c>
       <c r="O32">
-        <v>37.947542325</v>
+        <v>37.8715604025</v>
       </c>
       <c r="P32">
-        <v>192.037562675</v>
+        <v>191.6530480975</v>
       </c>
       <c r="Q32">
-        <v>296.237562675</v>
+        <v>295.8530480975</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09151622352364351</v>
+        <v>0.0920982672480333</v>
       </c>
       <c r="T32">
-        <v>0.8910942880379094</v>
+        <v>0.9024394035836809</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>17.64761874773569</v>
+        <v>17.07834072361518</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07656795940114297</v>
+        <v>0.07647441233573549</v>
       </c>
       <c r="C33">
-        <v>636.8469240040076</v>
+        <v>627.8633513289878</v>
       </c>
       <c r="D33">
-        <v>416.7519240040078</v>
+        <v>416.9233513289878</v>
       </c>
       <c r="E33">
-        <v>268.605</v>
+        <v>277.76</v>
       </c>
       <c r="F33">
-        <v>283.805</v>
+        <v>292.96</v>
       </c>
       <c r="G33">
         <v>503.9</v>
@@ -4249,28 +4249,28 @@
         <v>243.8</v>
       </c>
       <c r="M33">
-        <v>14.2753915</v>
+        <v>14.735888</v>
       </c>
       <c r="N33">
-        <v>229.5246085</v>
+        <v>229.064112</v>
       </c>
       <c r="O33">
-        <v>37.8715604025</v>
+        <v>37.79557848</v>
       </c>
       <c r="P33">
-        <v>191.6530480975</v>
+        <v>191.26853352</v>
       </c>
       <c r="Q33">
-        <v>295.8530480975</v>
+        <v>295.46853352</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0920982672480333</v>
+        <v>0.09269742990549339</v>
       </c>
       <c r="T33">
-        <v>0.9024394035836809</v>
+        <v>0.9141181989984458</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>17.07834072361518</v>
+        <v>16.54464257600221</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4295,22 +4295,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07647441233573549</v>
+        <v>0.076380865270328</v>
       </c>
       <c r="C34">
-        <v>627.8633513289878</v>
+        <v>618.8799197423193</v>
       </c>
       <c r="D34">
-        <v>416.9233513289878</v>
+        <v>417.0949197423194</v>
       </c>
       <c r="E34">
-        <v>277.76</v>
+        <v>286.915</v>
       </c>
       <c r="F34">
-        <v>292.96</v>
+        <v>302.115</v>
       </c>
       <c r="G34">
         <v>503.9</v>
@@ -4331,28 +4331,28 @@
         <v>243.8</v>
       </c>
       <c r="M34">
-        <v>14.735888</v>
+        <v>15.1963845</v>
       </c>
       <c r="N34">
-        <v>229.064112</v>
+        <v>228.6036155</v>
       </c>
       <c r="O34">
-        <v>37.79557848</v>
+        <v>37.7195965575</v>
       </c>
       <c r="P34">
-        <v>191.26853352</v>
+        <v>190.8840189425</v>
       </c>
       <c r="Q34">
-        <v>295.46853352</v>
+        <v>295.0840189425</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09269742990549339</v>
+        <v>0.09331447801541495</v>
       </c>
       <c r="T34">
-        <v>0.9141181989984458</v>
+        <v>0.9261456151718602</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>16.54464257600221</v>
+        <v>16.04328977066881</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4377,22 +4377,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.076380865270328</v>
+        <v>0.07628731820492053</v>
       </c>
       <c r="C35">
-        <v>618.8799197423193</v>
+        <v>609.8966294182521</v>
       </c>
       <c r="D35">
-        <v>417.0949197423194</v>
+        <v>417.2666294182521</v>
       </c>
       <c r="E35">
-        <v>286.915</v>
+        <v>296.0700000000001</v>
       </c>
       <c r="F35">
-        <v>302.115</v>
+        <v>311.27</v>
       </c>
       <c r="G35">
         <v>503.9</v>
@@ -4413,28 +4413,28 @@
         <v>243.8</v>
       </c>
       <c r="M35">
-        <v>15.1963845</v>
+        <v>15.656881</v>
       </c>
       <c r="N35">
-        <v>228.6036155</v>
+        <v>228.143119</v>
       </c>
       <c r="O35">
-        <v>37.7195965575</v>
+        <v>37.64361463500001</v>
       </c>
       <c r="P35">
-        <v>190.8840189425</v>
+        <v>190.499504365</v>
       </c>
       <c r="Q35">
-        <v>295.0840189425</v>
+        <v>294.699504365</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09331447801541495</v>
+        <v>0.09395022455290991</v>
       </c>
       <c r="T35">
-        <v>0.9261456151718602</v>
+        <v>0.9385374985020449</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>16.04328977066881</v>
+        <v>15.5714283068256</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4459,22 +4459,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07628731820492053</v>
+        <v>0.07619377113951306</v>
       </c>
       <c r="C36">
-        <v>609.8966294182521</v>
+        <v>600.9134805313229</v>
       </c>
       <c r="D36">
-        <v>417.2666294182521</v>
+        <v>417.4384805313229</v>
       </c>
       <c r="E36">
-        <v>296.0700000000001</v>
+        <v>305.225</v>
       </c>
       <c r="F36">
-        <v>311.27</v>
+        <v>320.425</v>
       </c>
       <c r="G36">
         <v>503.9</v>
@@ -4495,28 +4495,28 @@
         <v>243.8</v>
       </c>
       <c r="M36">
-        <v>15.656881</v>
+        <v>16.1173775</v>
       </c>
       <c r="N36">
-        <v>228.143119</v>
+        <v>227.6826225</v>
       </c>
       <c r="O36">
-        <v>37.64361463500001</v>
+        <v>37.5676327125</v>
       </c>
       <c r="P36">
-        <v>190.499504365</v>
+        <v>190.1149897875</v>
       </c>
       <c r="Q36">
-        <v>294.699504365</v>
+        <v>294.3149897875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09395022455290991</v>
+        <v>0.0946055325223278</v>
       </c>
       <c r="T36">
-        <v>0.9385374985020449</v>
+        <v>0.9513106705500816</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>15.5714283068256</v>
+        <v>15.12653035520202</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4541,22 +4541,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07619377113951306</v>
+        <v>0.07610022407410558</v>
       </c>
       <c r="C37">
-        <v>600.9134805313229</v>
+        <v>591.9304732563561</v>
       </c>
       <c r="D37">
-        <v>417.4384805313229</v>
+        <v>417.6104732563562</v>
       </c>
       <c r="E37">
-        <v>305.225</v>
+        <v>314.3800000000001</v>
       </c>
       <c r="F37">
-        <v>320.425</v>
+        <v>329.58</v>
       </c>
       <c r="G37">
         <v>503.9</v>
@@ -4577,28 +4577,28 @@
         <v>243.8</v>
       </c>
       <c r="M37">
-        <v>16.1173775</v>
+        <v>16.577874</v>
       </c>
       <c r="N37">
-        <v>227.6826225</v>
+        <v>227.222126</v>
       </c>
       <c r="O37">
-        <v>37.5676327125</v>
+        <v>37.49165079</v>
       </c>
       <c r="P37">
-        <v>190.1149897875</v>
+        <v>189.73047521</v>
       </c>
       <c r="Q37">
-        <v>294.3149897875</v>
+        <v>293.93047521</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0946055325223278</v>
+        <v>0.09528131886578997</v>
       </c>
       <c r="T37">
-        <v>0.9513106705500816</v>
+        <v>0.9644830042246191</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>15.12653035520202</v>
+        <v>14.7063489564464</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4623,22 +4623,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07610022407410558</v>
+        <v>0.07600667700869811</v>
       </c>
       <c r="C38">
-        <v>591.9304732563562</v>
+        <v>582.9476077684648</v>
       </c>
       <c r="D38">
-        <v>417.6104732563562</v>
+        <v>417.7826077684649</v>
       </c>
       <c r="E38">
-        <v>314.38</v>
+        <v>323.535</v>
       </c>
       <c r="F38">
-        <v>329.58</v>
+        <v>338.735</v>
       </c>
       <c r="G38">
         <v>503.9</v>
@@ -4659,28 +4659,28 @@
         <v>243.8</v>
       </c>
       <c r="M38">
-        <v>16.577874</v>
+        <v>17.0383705</v>
       </c>
       <c r="N38">
-        <v>227.222126</v>
+        <v>226.7616295</v>
       </c>
       <c r="O38">
-        <v>37.49165079</v>
+        <v>37.4156688675</v>
       </c>
       <c r="P38">
-        <v>189.73047521</v>
+        <v>189.3459606325</v>
       </c>
       <c r="Q38">
-        <v>293.93047521</v>
+        <v>293.5459606325</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09528131886578997</v>
+        <v>0.09597855874396526</v>
       </c>
       <c r="T38">
-        <v>0.9644830042246191</v>
+        <v>0.9780735072221579</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>14.70634895644641</v>
+        <v>14.30888006573164</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4705,22 +4705,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07600667700869811</v>
+        <v>0.07591312994329064</v>
       </c>
       <c r="C39">
-        <v>582.9476077684648</v>
+        <v>573.9648842430503</v>
       </c>
       <c r="D39">
-        <v>417.7826077684649</v>
+        <v>417.9548842430503</v>
       </c>
       <c r="E39">
-        <v>323.535</v>
+        <v>332.69</v>
       </c>
       <c r="F39">
-        <v>338.735</v>
+        <v>347.89</v>
       </c>
       <c r="G39">
         <v>503.9</v>
@@ -4741,28 +4741,28 @@
         <v>243.8</v>
       </c>
       <c r="M39">
-        <v>17.0383705</v>
+        <v>17.498867</v>
       </c>
       <c r="N39">
-        <v>226.7616295</v>
+        <v>226.301133</v>
       </c>
       <c r="O39">
-        <v>37.4156688675</v>
+        <v>37.339686945</v>
       </c>
       <c r="P39">
-        <v>189.3459606325</v>
+        <v>188.961446055</v>
       </c>
       <c r="Q39">
-        <v>293.5459606325</v>
+        <v>293.161446055</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09597855874396526</v>
+        <v>0.09669829023111393</v>
       </c>
       <c r="T39">
-        <v>0.9780735072221579</v>
+        <v>0.992102413542198</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>14.30888006573164</v>
+        <v>13.93233059031765</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4787,22 +4787,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07591312994329064</v>
+        <v>0.07581958287788315</v>
       </c>
       <c r="C40">
-        <v>573.9648842430503</v>
+        <v>564.9823028558037</v>
       </c>
       <c r="D40">
-        <v>417.9548842430503</v>
+        <v>418.1273028558037</v>
       </c>
       <c r="E40">
-        <v>332.69</v>
+        <v>341.845</v>
       </c>
       <c r="F40">
-        <v>347.89</v>
+        <v>357.045</v>
       </c>
       <c r="G40">
         <v>503.9</v>
@@ -4823,28 +4823,28 @@
         <v>243.8</v>
       </c>
       <c r="M40">
-        <v>17.498867</v>
+        <v>17.9593635</v>
       </c>
       <c r="N40">
-        <v>226.301133</v>
+        <v>225.8406365</v>
       </c>
       <c r="O40">
-        <v>37.339686945</v>
+        <v>37.26370502250001</v>
       </c>
       <c r="P40">
-        <v>188.961446055</v>
+        <v>188.5769314775</v>
       </c>
       <c r="Q40">
-        <v>293.161446055</v>
+        <v>292.7769314775</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09669829023111393</v>
+        <v>0.09744161947193959</v>
       </c>
       <c r="T40">
-        <v>0.992102413542198</v>
+        <v>1.006591284003879</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.93233059031765</v>
+        <v>13.57509134441207</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4869,22 +4869,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07581958287788315</v>
+        <v>0.07572603581247567</v>
       </c>
       <c r="C41">
-        <v>564.9823028558037</v>
+        <v>555.9998637827061</v>
       </c>
       <c r="D41">
-        <v>418.1273028558037</v>
+        <v>418.2998637827062</v>
       </c>
       <c r="E41">
-        <v>341.845</v>
+        <v>351.0000000000001</v>
       </c>
       <c r="F41">
-        <v>357.045</v>
+        <v>366.2</v>
       </c>
       <c r="G41">
         <v>503.9</v>
@@ -4905,28 +4905,28 @@
         <v>243.8</v>
       </c>
       <c r="M41">
-        <v>17.9593635</v>
+        <v>18.41986</v>
       </c>
       <c r="N41">
-        <v>225.8406365</v>
+        <v>225.38014</v>
       </c>
       <c r="O41">
-        <v>37.26370502250001</v>
+        <v>37.18772310000001</v>
       </c>
       <c r="P41">
-        <v>188.5769314775</v>
+        <v>188.1924169</v>
       </c>
       <c r="Q41">
-        <v>292.7769314775</v>
+        <v>292.3924169</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09744161947193959</v>
+        <v>0.09820972635412613</v>
       </c>
       <c r="T41">
-        <v>1.006591284003879</v>
+        <v>1.021563116814282</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>13.57509134441207</v>
+        <v>13.23571406080177</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4951,22 +4951,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07572603581247567</v>
+        <v>0.0756324887470682</v>
       </c>
       <c r="C42">
-        <v>555.9998637827061</v>
+        <v>547.0175672000291</v>
       </c>
       <c r="D42">
-        <v>418.2998637827062</v>
+        <v>418.4725672000292</v>
       </c>
       <c r="E42">
-        <v>351.0000000000001</v>
+        <v>360.155</v>
       </c>
       <c r="F42">
-        <v>366.2</v>
+        <v>375.355</v>
       </c>
       <c r="G42">
         <v>503.9</v>
@@ -4987,28 +4987,28 @@
         <v>243.8</v>
       </c>
       <c r="M42">
-        <v>18.41986</v>
+        <v>18.8803565</v>
       </c>
       <c r="N42">
-        <v>225.38014</v>
+        <v>224.9196435</v>
       </c>
       <c r="O42">
-        <v>37.18772310000001</v>
+        <v>37.1117411775</v>
       </c>
       <c r="P42">
-        <v>188.1924169</v>
+        <v>187.8079023225</v>
       </c>
       <c r="Q42">
-        <v>292.3924169</v>
+        <v>292.0079023225</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09820972635412613</v>
+        <v>0.09900387075774271</v>
       </c>
       <c r="T42">
-        <v>1.021563116814282</v>
+        <v>1.037042469380971</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>13.23571406080177</v>
+        <v>12.91289176663587</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5033,22 +5033,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0756324887470682</v>
+        <v>0.07606499168166071</v>
       </c>
       <c r="C43">
-        <v>547.0175672000291</v>
+        <v>537.0652871844693</v>
       </c>
       <c r="D43">
-        <v>418.4725672000292</v>
+        <v>417.6752871844693</v>
       </c>
       <c r="E43">
-        <v>360.155</v>
+        <v>369.3100000000001</v>
       </c>
       <c r="F43">
-        <v>375.355</v>
+        <v>384.51</v>
       </c>
       <c r="G43">
         <v>503.9</v>
@@ -5069,45 +5069,45 @@
         <v>243.8</v>
       </c>
       <c r="M43">
-        <v>18.8803565</v>
+        <v>19.917618</v>
       </c>
       <c r="N43">
-        <v>224.9196435</v>
+        <v>223.882382</v>
       </c>
       <c r="O43">
-        <v>37.1117411775</v>
+        <v>36.94059303</v>
       </c>
       <c r="P43">
-        <v>187.8079023225</v>
+        <v>186.94178897</v>
       </c>
       <c r="Q43">
-        <v>292.0079023225</v>
+        <v>291.14178897</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09900387075774271</v>
+        <v>0.09982539945113916</v>
       </c>
       <c r="T43">
-        <v>1.037042469380971</v>
+        <v>1.05305559272582</v>
       </c>
       <c r="U43">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V43">
         <v>0.165</v>
       </c>
       <c r="W43">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y43">
-        <v>12.91289176663587</v>
+        <v>12.24041951201193</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5115,22 +5115,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07606499168166073</v>
+        <v>0.07598396961625324</v>
       </c>
       <c r="C44">
-        <v>537.0652871844692</v>
+        <v>528.0594126965029</v>
       </c>
       <c r="D44">
-        <v>417.6752871844692</v>
+        <v>417.8244126965029</v>
       </c>
       <c r="E44">
-        <v>369.31</v>
+        <v>378.465</v>
       </c>
       <c r="F44">
-        <v>384.51</v>
+        <v>393.665</v>
       </c>
       <c r="G44">
         <v>503.9</v>
@@ -5151,28 +5151,28 @@
         <v>243.8</v>
       </c>
       <c r="M44">
-        <v>19.917618</v>
+        <v>20.391847</v>
       </c>
       <c r="N44">
-        <v>223.882382</v>
+        <v>223.408153</v>
       </c>
       <c r="O44">
-        <v>36.94059303</v>
+        <v>36.862345245</v>
       </c>
       <c r="P44">
-        <v>186.94178897</v>
+        <v>186.545807755</v>
       </c>
       <c r="Q44">
-        <v>291.14178897</v>
+        <v>290.745807755</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09982539945113916</v>
+        <v>0.100675753712725</v>
       </c>
       <c r="T44">
-        <v>1.05305559272582</v>
+        <v>1.069630580047683</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>12.24041951201193</v>
+        <v>11.95575859312793</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5197,22 +5197,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07598396961625324</v>
+        <v>0.07590294755084576</v>
       </c>
       <c r="C45">
-        <v>528.0594126965029</v>
+        <v>519.0536447332067</v>
       </c>
       <c r="D45">
-        <v>417.8244126965029</v>
+        <v>417.9736447332068</v>
       </c>
       <c r="E45">
-        <v>378.465</v>
+        <v>387.62</v>
       </c>
       <c r="F45">
-        <v>393.665</v>
+        <v>402.82</v>
       </c>
       <c r="G45">
         <v>503.9</v>
@@ -5233,28 +5233,28 @@
         <v>243.8</v>
       </c>
       <c r="M45">
-        <v>20.391847</v>
+        <v>20.866076</v>
       </c>
       <c r="N45">
-        <v>223.408153</v>
+        <v>222.933924</v>
       </c>
       <c r="O45">
-        <v>36.862345245</v>
+        <v>36.78409746000001</v>
       </c>
       <c r="P45">
-        <v>186.545807755</v>
+        <v>186.14982654</v>
       </c>
       <c r="Q45">
-        <v>290.745807755</v>
+        <v>290.34982654</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.100675753712725</v>
+        <v>0.1015564777693674</v>
       </c>
       <c r="T45">
-        <v>1.069630580047683</v>
+        <v>1.086797531202468</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.95575859312793</v>
+        <v>11.68403680692048</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07590294755084576</v>
+        <v>0.07582192548543829</v>
       </c>
       <c r="C46">
-        <v>519.0536447332067</v>
+        <v>510.0479834087621</v>
       </c>
       <c r="D46">
-        <v>417.9736447332068</v>
+        <v>418.1229834087621</v>
       </c>
       <c r="E46">
-        <v>387.62</v>
+        <v>396.775</v>
       </c>
       <c r="F46">
-        <v>402.82</v>
+        <v>411.975</v>
       </c>
       <c r="G46">
         <v>503.9</v>
@@ -5315,28 +5315,28 @@
         <v>243.8</v>
       </c>
       <c r="M46">
-        <v>20.866076</v>
+        <v>21.340305</v>
       </c>
       <c r="N46">
-        <v>222.933924</v>
+        <v>222.459695</v>
       </c>
       <c r="O46">
-        <v>36.78409746000001</v>
+        <v>36.705849675</v>
       </c>
       <c r="P46">
-        <v>186.14982654</v>
+        <v>185.753845325</v>
       </c>
       <c r="Q46">
-        <v>290.34982654</v>
+        <v>289.953845325</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1015564777693674</v>
+        <v>0.1024692281553423</v>
       </c>
       <c r="T46">
-        <v>1.086797531202468</v>
+        <v>1.104588735126519</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.68403680692048</v>
+        <v>11.42439154454447</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5361,22 +5361,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07582192548543829</v>
+        <v>0.07574090342003081</v>
       </c>
       <c r="C47">
-        <v>510.0479834087621</v>
+        <v>501.0424288375135</v>
       </c>
       <c r="D47">
-        <v>418.1229834087621</v>
+        <v>418.2724288375135</v>
       </c>
       <c r="E47">
-        <v>396.775</v>
+        <v>405.93</v>
       </c>
       <c r="F47">
-        <v>411.975</v>
+        <v>421.13</v>
       </c>
       <c r="G47">
         <v>503.9</v>
@@ -5397,28 +5397,28 @@
         <v>243.8</v>
       </c>
       <c r="M47">
-        <v>21.340305</v>
+        <v>21.814534</v>
       </c>
       <c r="N47">
-        <v>222.459695</v>
+        <v>221.985466</v>
       </c>
       <c r="O47">
-        <v>36.705849675</v>
+        <v>36.62760189</v>
       </c>
       <c r="P47">
-        <v>185.753845325</v>
+        <v>185.35786411</v>
       </c>
       <c r="Q47">
-        <v>289.953845325</v>
+        <v>289.55786411</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1024692281553423</v>
+        <v>0.1034157841111682</v>
       </c>
       <c r="T47">
-        <v>1.104588735126519</v>
+        <v>1.123038872529239</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.42439154454447</v>
+        <v>11.17603520661959</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5443,22 +5443,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07574090342003081</v>
+        <v>0.07565988135462333</v>
       </c>
       <c r="C48">
-        <v>501.0424288375135</v>
+        <v>492.0369811339688</v>
       </c>
       <c r="D48">
-        <v>418.2724288375135</v>
+        <v>418.4219811339689</v>
       </c>
       <c r="E48">
-        <v>405.93</v>
+        <v>415.085</v>
       </c>
       <c r="F48">
-        <v>421.13</v>
+        <v>430.285</v>
       </c>
       <c r="G48">
         <v>503.9</v>
@@ -5479,28 +5479,28 @@
         <v>243.8</v>
       </c>
       <c r="M48">
-        <v>21.814534</v>
+        <v>22.288763</v>
       </c>
       <c r="N48">
-        <v>221.985466</v>
+        <v>221.511237</v>
       </c>
       <c r="O48">
-        <v>36.62760189</v>
+        <v>36.54935410500001</v>
       </c>
       <c r="P48">
-        <v>185.35786411</v>
+        <v>184.961882895</v>
       </c>
       <c r="Q48">
-        <v>289.55786411</v>
+        <v>289.161882895</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1034157841111682</v>
+        <v>0.1043980591596667</v>
       </c>
       <c r="T48">
-        <v>1.123038872529239</v>
+        <v>1.142185241532061</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>11.17603520661959</v>
+        <v>10.93824722350002</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5525,22 +5525,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07565988135462333</v>
+        <v>0.07557885928921586</v>
       </c>
       <c r="C49">
-        <v>492.0369811339688</v>
+        <v>483.0316404128</v>
       </c>
       <c r="D49">
-        <v>418.4219811339689</v>
+        <v>418.5716404128001</v>
       </c>
       <c r="E49">
-        <v>415.085</v>
+        <v>424.2400000000001</v>
       </c>
       <c r="F49">
-        <v>430.285</v>
+        <v>439.4400000000001</v>
       </c>
       <c r="G49">
         <v>503.9</v>
@@ -5561,28 +5561,28 @@
         <v>243.8</v>
       </c>
       <c r="M49">
-        <v>22.288763</v>
+        <v>22.762992</v>
       </c>
       <c r="N49">
-        <v>221.511237</v>
+        <v>221.037008</v>
       </c>
       <c r="O49">
-        <v>36.54935410500001</v>
+        <v>36.47110632</v>
       </c>
       <c r="P49">
-        <v>184.961882895</v>
+        <v>184.56590168</v>
       </c>
       <c r="Q49">
-        <v>289.161882895</v>
+        <v>288.76590168</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1043980591596667</v>
+        <v>0.1054181140177228</v>
       </c>
       <c r="T49">
-        <v>1.142185241532061</v>
+        <v>1.162068009342684</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.93824722350002</v>
+        <v>10.71036707301044</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5607,22 +5607,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07557885928921584</v>
+        <v>0.07549783722380837</v>
       </c>
       <c r="C50">
-        <v>483.0316404128001</v>
+        <v>474.0264067888434</v>
       </c>
       <c r="D50">
-        <v>418.5716404128001</v>
+        <v>418.7214067888434</v>
       </c>
       <c r="E50">
-        <v>424.24</v>
+        <v>433.395</v>
       </c>
       <c r="F50">
-        <v>439.44</v>
+        <v>448.595</v>
       </c>
       <c r="G50">
         <v>503.9</v>
@@ -5643,28 +5643,28 @@
         <v>243.8</v>
       </c>
       <c r="M50">
-        <v>22.762992</v>
+        <v>23.237221</v>
       </c>
       <c r="N50">
-        <v>221.037008</v>
+        <v>220.562779</v>
       </c>
       <c r="O50">
-        <v>36.47110632</v>
+        <v>36.392858535</v>
       </c>
       <c r="P50">
-        <v>184.56590168</v>
+        <v>184.169920465</v>
       </c>
       <c r="Q50">
-        <v>288.76590168</v>
+        <v>288.369920465</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1054181140177228</v>
+        <v>0.1064781710270752</v>
       </c>
       <c r="T50">
-        <v>1.162068009342684</v>
+        <v>1.182730493538037</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.71036707301044</v>
+        <v>10.49178815315308</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5689,22 +5689,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07549783722380837</v>
+        <v>0.0754168151584009</v>
       </c>
       <c r="C51">
-        <v>474.0264067888434</v>
+        <v>465.0212803770987</v>
       </c>
       <c r="D51">
-        <v>418.7214067888434</v>
+        <v>418.8712803770987</v>
       </c>
       <c r="E51">
-        <v>433.395</v>
+        <v>442.55</v>
       </c>
       <c r="F51">
-        <v>448.595</v>
+        <v>457.75</v>
       </c>
       <c r="G51">
         <v>503.9</v>
@@ -5725,28 +5725,28 @@
         <v>243.8</v>
       </c>
       <c r="M51">
-        <v>23.237221</v>
+        <v>23.71145</v>
       </c>
       <c r="N51">
-        <v>220.562779</v>
+        <v>220.08855</v>
       </c>
       <c r="O51">
-        <v>36.392858535</v>
+        <v>36.31461075</v>
       </c>
       <c r="P51">
-        <v>184.169920465</v>
+        <v>183.77393925</v>
       </c>
       <c r="Q51">
-        <v>288.369920465</v>
+        <v>287.97393925</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1064781710270752</v>
+        <v>0.1075806303168018</v>
       </c>
       <c r="T51">
-        <v>1.182730493538037</v>
+        <v>1.204219477101204</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.49178815315308</v>
+        <v>10.28195239009002</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5771,22 +5771,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0754168151584009</v>
+        <v>0.0753357930929934</v>
       </c>
       <c r="C52">
-        <v>465.0212803770987</v>
+        <v>456.0162612927317</v>
       </c>
       <c r="D52">
-        <v>418.8712803770987</v>
+        <v>419.0212612927317</v>
       </c>
       <c r="E52">
-        <v>442.55</v>
+        <v>451.705</v>
       </c>
       <c r="F52">
-        <v>457.75</v>
+        <v>466.905</v>
       </c>
       <c r="G52">
         <v>503.9</v>
@@ -5807,28 +5807,28 @@
         <v>243.8</v>
       </c>
       <c r="M52">
-        <v>23.71145</v>
+        <v>24.185679</v>
       </c>
       <c r="N52">
-        <v>220.08855</v>
+        <v>219.614321</v>
       </c>
       <c r="O52">
-        <v>36.31461075</v>
+        <v>36.236362965</v>
       </c>
       <c r="P52">
-        <v>183.77393925</v>
+        <v>183.377958035</v>
       </c>
       <c r="Q52">
-        <v>287.97393925</v>
+        <v>287.577958035</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1075806303168018</v>
+        <v>0.1087280879448845</v>
       </c>
       <c r="T52">
-        <v>1.204219477101204</v>
+        <v>1.226585562034297</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>10.28195239009002</v>
+        <v>10.08034548048041</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5853,22 +5853,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0753357930929934</v>
+        <v>0.07525477102758593</v>
       </c>
       <c r="C53">
-        <v>456.0162612927317</v>
+        <v>447.0113496510721</v>
       </c>
       <c r="D53">
-        <v>419.0212612927317</v>
+        <v>419.1713496510721</v>
       </c>
       <c r="E53">
-        <v>451.705</v>
+        <v>460.86</v>
       </c>
       <c r="F53">
-        <v>466.905</v>
+        <v>476.06</v>
       </c>
       <c r="G53">
         <v>503.9</v>
@@ -5889,28 +5889,28 @@
         <v>243.8</v>
       </c>
       <c r="M53">
-        <v>24.185679</v>
+        <v>24.659908</v>
       </c>
       <c r="N53">
-        <v>219.614321</v>
+        <v>219.140092</v>
       </c>
       <c r="O53">
-        <v>36.236362965</v>
+        <v>36.15811518</v>
       </c>
       <c r="P53">
-        <v>183.377958035</v>
+        <v>182.98197682</v>
       </c>
       <c r="Q53">
-        <v>287.577958035</v>
+        <v>287.18197682</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1087280879448845</v>
+        <v>0.1099233563074707</v>
       </c>
       <c r="T53">
-        <v>1.226585562034297</v>
+        <v>1.249883567172935</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>10.08034548048041</v>
+        <v>9.886492682778867</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5935,22 +5935,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07525477102758593</v>
+        <v>0.07592608396217845</v>
       </c>
       <c r="C54">
-        <v>447.0113496510721</v>
+        <v>436.6160196197319</v>
       </c>
       <c r="D54">
-        <v>419.1713496510721</v>
+        <v>417.931019619732</v>
       </c>
       <c r="E54">
-        <v>460.86</v>
+        <v>470.015</v>
       </c>
       <c r="F54">
-        <v>476.06</v>
+        <v>485.215</v>
       </c>
       <c r="G54">
         <v>503.9</v>
@@ -5971,45 +5971,45 @@
         <v>243.8</v>
       </c>
       <c r="M54">
-        <v>24.659908</v>
+        <v>25.9590025</v>
       </c>
       <c r="N54">
-        <v>219.140092</v>
+        <v>217.8409975</v>
       </c>
       <c r="O54">
-        <v>36.15811518</v>
+        <v>35.94376458750001</v>
       </c>
       <c r="P54">
-        <v>182.98197682</v>
+        <v>181.8972329125</v>
       </c>
       <c r="Q54">
-        <v>287.18197682</v>
+        <v>286.0972329125</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1099233563074707</v>
+        <v>0.1111694871535712</v>
       </c>
       <c r="T54">
-        <v>1.249883567172935</v>
+        <v>1.274172976785557</v>
       </c>
       <c r="U54">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V54">
         <v>0.165</v>
       </c>
       <c r="W54">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>9.886492682778867</v>
+        <v>9.391732213131071</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6017,22 +6017,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07592608396217845</v>
+        <v>0.07585925689677096</v>
       </c>
       <c r="C55">
-        <v>436.6160196197319</v>
+        <v>427.5841614471586</v>
       </c>
       <c r="D55">
-        <v>417.931019619732</v>
+        <v>418.0541614471587</v>
       </c>
       <c r="E55">
-        <v>470.015</v>
+        <v>479.17</v>
       </c>
       <c r="F55">
-        <v>485.215</v>
+        <v>494.37</v>
       </c>
       <c r="G55">
         <v>503.9</v>
@@ -6053,28 +6053,28 @@
         <v>243.8</v>
       </c>
       <c r="M55">
-        <v>25.9590025</v>
+        <v>26.448795</v>
       </c>
       <c r="N55">
-        <v>217.8409975</v>
+        <v>217.351205</v>
       </c>
       <c r="O55">
-        <v>35.94376458750001</v>
+        <v>35.862948825</v>
       </c>
       <c r="P55">
-        <v>181.8972329125</v>
+        <v>181.488256175</v>
       </c>
       <c r="Q55">
-        <v>286.0972329125</v>
+        <v>285.688256175</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1111694871535712</v>
+        <v>0.112469797601676</v>
       </c>
       <c r="T55">
-        <v>1.274172976785557</v>
+        <v>1.299518447685685</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>9.391732213131071</v>
+        <v>9.217811246221236</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6099,22 +6099,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07585925689677096</v>
+        <v>0.0757924298313635</v>
       </c>
       <c r="C56">
-        <v>427.5841614471586</v>
+        <v>418.55237586254</v>
       </c>
       <c r="D56">
-        <v>418.0541614471587</v>
+        <v>418.1773758625401</v>
       </c>
       <c r="E56">
-        <v>479.17</v>
+        <v>488.325</v>
       </c>
       <c r="F56">
-        <v>494.37</v>
+        <v>503.525</v>
       </c>
       <c r="G56">
         <v>503.9</v>
@@ -6135,28 +6135,28 @@
         <v>243.8</v>
       </c>
       <c r="M56">
-        <v>26.448795</v>
+        <v>26.9385875</v>
       </c>
       <c r="N56">
-        <v>217.351205</v>
+        <v>216.8614125</v>
       </c>
       <c r="O56">
-        <v>35.862948825</v>
+        <v>35.7821330625</v>
       </c>
       <c r="P56">
-        <v>181.488256175</v>
+        <v>181.0792794375</v>
       </c>
       <c r="Q56">
-        <v>285.688256175</v>
+        <v>285.2792794375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.112469797601676</v>
+        <v>0.1138278996252522</v>
       </c>
       <c r="T56">
-        <v>1.299518447685685</v>
+        <v>1.325990383959152</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>9.217811246221236</v>
+        <v>9.050214678108123</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6181,22 +6181,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0757924298313635</v>
+        <v>0.07572560276595602</v>
       </c>
       <c r="C57">
-        <v>418.55237586254</v>
+        <v>409.5206629300773</v>
       </c>
       <c r="D57">
-        <v>418.1773758625401</v>
+        <v>418.3006629300774</v>
       </c>
       <c r="E57">
-        <v>488.325</v>
+        <v>497.4800000000001</v>
       </c>
       <c r="F57">
-        <v>503.525</v>
+        <v>512.6800000000001</v>
       </c>
       <c r="G57">
         <v>503.9</v>
@@ -6217,28 +6217,28 @@
         <v>243.8</v>
       </c>
       <c r="M57">
-        <v>26.9385875</v>
+        <v>27.42838</v>
       </c>
       <c r="N57">
-        <v>216.8614125</v>
+        <v>216.37162</v>
       </c>
       <c r="O57">
-        <v>35.7821330625</v>
+        <v>35.7013173</v>
       </c>
       <c r="P57">
-        <v>181.0792794375</v>
+        <v>180.6703027</v>
       </c>
       <c r="Q57">
-        <v>285.2792794375</v>
+        <v>284.8703027</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1138278996252522</v>
+        <v>0.115247733558991</v>
       </c>
       <c r="T57">
-        <v>1.325990383959152</v>
+        <v>1.353665590063231</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>9.050214678108123</v>
+        <v>8.888603701713334</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6263,22 +6263,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07572560276595602</v>
+        <v>0.07565877570054853</v>
       </c>
       <c r="C58">
-        <v>409.5206629300773</v>
+        <v>400.4890227140475</v>
       </c>
       <c r="D58">
-        <v>418.3006629300774</v>
+        <v>418.4240227140475</v>
       </c>
       <c r="E58">
-        <v>497.4800000000001</v>
+        <v>506.635</v>
       </c>
       <c r="F58">
-        <v>512.6800000000001</v>
+        <v>521.835</v>
       </c>
       <c r="G58">
         <v>503.9</v>
@@ -6299,28 +6299,28 @@
         <v>243.8</v>
       </c>
       <c r="M58">
-        <v>27.42838</v>
+        <v>27.9181725</v>
       </c>
       <c r="N58">
-        <v>216.37162</v>
+        <v>215.8818275</v>
       </c>
       <c r="O58">
-        <v>35.7013173</v>
+        <v>35.6205015375</v>
       </c>
       <c r="P58">
-        <v>180.6703027</v>
+        <v>180.2613259625</v>
       </c>
       <c r="Q58">
-        <v>284.8703027</v>
+        <v>284.4613259625</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.115247733558991</v>
+        <v>0.1167336062803454</v>
       </c>
       <c r="T58">
-        <v>1.353665590063231</v>
+        <v>1.382628015055872</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.888603701713334</v>
+        <v>8.732663285893803</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07565877570054853</v>
+        <v>0.07559194863514106</v>
       </c>
       <c r="C59">
-        <v>400.4890227140475</v>
+        <v>391.4574552788031</v>
       </c>
       <c r="D59">
-        <v>418.4240227140475</v>
+        <v>418.5474552788031</v>
       </c>
       <c r="E59">
-        <v>506.635</v>
+        <v>515.79</v>
       </c>
       <c r="F59">
-        <v>521.835</v>
+        <v>530.99</v>
       </c>
       <c r="G59">
         <v>503.9</v>
@@ -6381,28 +6381,28 @@
         <v>243.8</v>
       </c>
       <c r="M59">
-        <v>27.9181725</v>
+        <v>28.407965</v>
       </c>
       <c r="N59">
-        <v>215.8818275</v>
+        <v>215.392035</v>
       </c>
       <c r="O59">
-        <v>35.6205015375</v>
+        <v>35.539685775</v>
       </c>
       <c r="P59">
-        <v>180.2613259625</v>
+        <v>179.852349225</v>
       </c>
       <c r="Q59">
-        <v>284.4613259625</v>
+        <v>284.052349225</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1167336062803454</v>
+        <v>0.118290234845574</v>
       </c>
       <c r="T59">
-        <v>1.382628015055872</v>
+        <v>1.412969603143401</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.732663285893803</v>
+        <v>8.582100125792186</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6427,22 +6427,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07559194863514107</v>
+        <v>0.07552512156973358</v>
       </c>
       <c r="C60">
-        <v>391.4574552788031</v>
+        <v>382.4259606887726</v>
       </c>
       <c r="D60">
-        <v>418.5474552788031</v>
+        <v>418.6709606887727</v>
       </c>
       <c r="E60">
-        <v>515.79</v>
+        <v>524.9449999999999</v>
       </c>
       <c r="F60">
-        <v>530.99</v>
+        <v>540.145</v>
       </c>
       <c r="G60">
         <v>503.9</v>
@@ -6463,28 +6463,28 @@
         <v>243.8</v>
       </c>
       <c r="M60">
-        <v>28.407965</v>
+        <v>28.8977575</v>
       </c>
       <c r="N60">
-        <v>215.392035</v>
+        <v>214.9022425</v>
       </c>
       <c r="O60">
-        <v>35.539685775</v>
+        <v>35.4588700125</v>
       </c>
       <c r="P60">
-        <v>179.852349225</v>
+        <v>179.4433724875</v>
       </c>
       <c r="Q60">
-        <v>284.052349225</v>
+        <v>283.6433724875</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.118290234845574</v>
+        <v>0.1199227965115453</v>
       </c>
       <c r="T60">
-        <v>1.412969603143401</v>
+        <v>1.444791268698613</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.582100125792186</v>
+        <v>8.436640801626217</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6509,22 +6509,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07552512156973358</v>
+        <v>0.07545829450432609</v>
       </c>
       <c r="C61">
-        <v>382.4259606887726</v>
+        <v>373.3945390084615</v>
       </c>
       <c r="D61">
-        <v>418.6709606887727</v>
+        <v>418.7945390084615</v>
       </c>
       <c r="E61">
-        <v>524.9449999999999</v>
+        <v>534.0999999999999</v>
       </c>
       <c r="F61">
-        <v>540.145</v>
+        <v>549.3</v>
       </c>
       <c r="G61">
         <v>503.9</v>
@@ -6545,28 +6545,28 @@
         <v>243.8</v>
       </c>
       <c r="M61">
-        <v>28.8977575</v>
+        <v>29.38755</v>
       </c>
       <c r="N61">
-        <v>214.9022425</v>
+        <v>214.41245</v>
       </c>
       <c r="O61">
-        <v>35.4588700125</v>
+        <v>35.37805425000001</v>
       </c>
       <c r="P61">
-        <v>179.4433724875</v>
+        <v>179.03439575</v>
       </c>
       <c r="Q61">
-        <v>283.6433724875</v>
+        <v>283.23439575</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1199227965115453</v>
+        <v>0.1216369862608152</v>
       </c>
       <c r="T61">
-        <v>1.444791268698613</v>
+        <v>1.478204017531587</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.436640801626217</v>
+        <v>8.296030121599113</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6591,22 +6591,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07545829450432609</v>
+        <v>0.07539146743891861</v>
       </c>
       <c r="C62">
-        <v>373.3945390084615</v>
+        <v>364.3631903024501</v>
       </c>
       <c r="D62">
-        <v>418.7945390084615</v>
+        <v>418.9181903024501</v>
       </c>
       <c r="E62">
-        <v>534.0999999999999</v>
+        <v>543.255</v>
       </c>
       <c r="F62">
-        <v>549.3</v>
+        <v>558.455</v>
       </c>
       <c r="G62">
         <v>503.9</v>
@@ -6627,28 +6627,28 @@
         <v>243.8</v>
       </c>
       <c r="M62">
-        <v>29.38755</v>
+        <v>29.8773425</v>
       </c>
       <c r="N62">
-        <v>214.41245</v>
+        <v>213.9226575</v>
       </c>
       <c r="O62">
-        <v>35.37805425000001</v>
+        <v>35.2972384875</v>
       </c>
       <c r="P62">
-        <v>179.03439575</v>
+        <v>178.6254190125</v>
       </c>
       <c r="Q62">
-        <v>283.23439575</v>
+        <v>282.8254190125</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1216369862608152</v>
+        <v>0.1234390831767144</v>
       </c>
       <c r="T62">
-        <v>1.478204017531587</v>
+        <v>1.513330240663687</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.296030121599113</v>
+        <v>8.160029627802405</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6673,22 +6673,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07539146743891861</v>
+        <v>0.07532464037351114</v>
       </c>
       <c r="C63">
-        <v>364.3631903024501</v>
+        <v>355.3319146353957</v>
       </c>
       <c r="D63">
-        <v>418.9181903024501</v>
+        <v>419.0419146353958</v>
       </c>
       <c r="E63">
-        <v>543.255</v>
+        <v>552.41</v>
       </c>
       <c r="F63">
-        <v>558.455</v>
+        <v>567.61</v>
       </c>
       <c r="G63">
         <v>503.9</v>
@@ -6709,28 +6709,28 @@
         <v>243.8</v>
       </c>
       <c r="M63">
-        <v>29.8773425</v>
+        <v>30.367135</v>
       </c>
       <c r="N63">
-        <v>213.9226575</v>
+        <v>213.432865</v>
       </c>
       <c r="O63">
-        <v>35.2972384875</v>
+        <v>35.21642272500001</v>
       </c>
       <c r="P63">
-        <v>178.6254190125</v>
+        <v>178.216442275</v>
       </c>
       <c r="Q63">
-        <v>282.8254190125</v>
+        <v>282.416442275</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1234390831767144</v>
+        <v>0.1253360272987135</v>
       </c>
       <c r="T63">
-        <v>1.513330240663687</v>
+        <v>1.550305212381688</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.160029627802405</v>
+        <v>8.028416246708819</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6755,22 +6755,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07532464037351114</v>
+        <v>0.07525781330810366</v>
       </c>
       <c r="C64">
-        <v>355.3319146353957</v>
+        <v>346.3007120720322</v>
       </c>
       <c r="D64">
-        <v>419.0419146353958</v>
+        <v>419.1657120720322</v>
       </c>
       <c r="E64">
-        <v>552.41</v>
+        <v>561.5649999999999</v>
       </c>
       <c r="F64">
-        <v>567.61</v>
+        <v>576.765</v>
       </c>
       <c r="G64">
         <v>503.9</v>
@@ -6791,28 +6791,28 @@
         <v>243.8</v>
       </c>
       <c r="M64">
-        <v>30.367135</v>
+        <v>30.8569275</v>
       </c>
       <c r="N64">
-        <v>213.432865</v>
+        <v>212.9430725</v>
       </c>
       <c r="O64">
-        <v>35.21642272500001</v>
+        <v>35.13560696250001</v>
       </c>
       <c r="P64">
-        <v>178.216442275</v>
+        <v>177.8074655375</v>
       </c>
       <c r="Q64">
-        <v>282.416442275</v>
+        <v>282.0074655375</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1253360272987135</v>
+        <v>0.1273355089408207</v>
       </c>
       <c r="T64">
-        <v>1.550305212381688</v>
+        <v>1.58927883121958</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>8.028416246708819</v>
+        <v>7.900981068189632</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6837,22 +6837,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07525781330810366</v>
+        <v>0.0751909862426962</v>
       </c>
       <c r="C65">
-        <v>346.3007120720322</v>
+        <v>337.2695826771695</v>
       </c>
       <c r="D65">
-        <v>419.1657120720322</v>
+        <v>419.2895826771695</v>
       </c>
       <c r="E65">
-        <v>561.5649999999999</v>
+        <v>570.7199999999999</v>
       </c>
       <c r="F65">
-        <v>576.765</v>
+        <v>585.92</v>
       </c>
       <c r="G65">
         <v>503.9</v>
@@ -6873,28 +6873,28 @@
         <v>243.8</v>
       </c>
       <c r="M65">
-        <v>30.8569275</v>
+        <v>31.34672</v>
       </c>
       <c r="N65">
-        <v>212.9430725</v>
+        <v>212.45328</v>
       </c>
       <c r="O65">
-        <v>35.13560696250001</v>
+        <v>35.0547912</v>
       </c>
       <c r="P65">
-        <v>177.8074655375</v>
+        <v>177.3984888</v>
       </c>
       <c r="Q65">
-        <v>282.0074655375</v>
+        <v>281.5984888</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1273355089408207</v>
+        <v>0.1294460728963783</v>
       </c>
       <c r="T65">
-        <v>1.58927883121958</v>
+        <v>1.630417651104022</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.900981068189632</v>
+        <v>7.777528238999169</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6919,22 +6919,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0751909862426962</v>
+        <v>0.07512415917728872</v>
       </c>
       <c r="C66">
-        <v>337.2695826771695</v>
+        <v>328.2385265156944</v>
       </c>
       <c r="D66">
-        <v>419.2895826771695</v>
+        <v>419.4135265156945</v>
       </c>
       <c r="E66">
-        <v>570.7199999999999</v>
+        <v>579.875</v>
       </c>
       <c r="F66">
-        <v>585.92</v>
+        <v>595.075</v>
       </c>
       <c r="G66">
         <v>503.9</v>
@@ -6955,28 +6955,28 @@
         <v>243.8</v>
       </c>
       <c r="M66">
-        <v>31.34672</v>
+        <v>31.8365125</v>
       </c>
       <c r="N66">
-        <v>212.45328</v>
+        <v>211.9634875</v>
       </c>
       <c r="O66">
-        <v>35.0547912</v>
+        <v>34.9739754375</v>
       </c>
       <c r="P66">
-        <v>177.3984888</v>
+        <v>176.9895120625</v>
       </c>
       <c r="Q66">
-        <v>281.5984888</v>
+        <v>281.1895120625</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1294460728963783</v>
+        <v>0.1316772405065392</v>
       </c>
       <c r="T66">
-        <v>1.630417651104022</v>
+        <v>1.673907260696147</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.777528238999169</v>
+        <v>7.657873958399181</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7001,22 +7001,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07512415917728872</v>
+        <v>0.07549821211188124</v>
       </c>
       <c r="C67">
-        <v>328.2385265156944</v>
+        <v>318.3907135749155</v>
       </c>
       <c r="D67">
-        <v>419.4135265156945</v>
+        <v>418.7207135749155</v>
       </c>
       <c r="E67">
-        <v>579.875</v>
+        <v>589.03</v>
       </c>
       <c r="F67">
-        <v>595.075</v>
+        <v>604.23</v>
       </c>
       <c r="G67">
         <v>503.9</v>
@@ -7037,45 +7037,45 @@
         <v>243.8</v>
       </c>
       <c r="M67">
-        <v>31.8365125</v>
+        <v>32.809689</v>
       </c>
       <c r="N67">
-        <v>211.9634875</v>
+        <v>210.990311</v>
       </c>
       <c r="O67">
-        <v>34.9739754375</v>
+        <v>34.81340131500001</v>
       </c>
       <c r="P67">
-        <v>176.9895120625</v>
+        <v>176.176909685</v>
       </c>
       <c r="Q67">
-        <v>281.1895120625</v>
+        <v>280.376909685</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1316772405065392</v>
+        <v>0.1340396532702389</v>
       </c>
       <c r="T67">
-        <v>1.673907260696147</v>
+        <v>1.719955082617219</v>
       </c>
       <c r="U67">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V67">
         <v>0.165</v>
       </c>
       <c r="W67">
-        <v>0.0446725</v>
+        <v>0.0453405</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y67">
-        <v>7.657873958399181</v>
+        <v>7.430731818274779</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7083,22 +7083,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07549821211188124</v>
+        <v>0.07543806504647375</v>
       </c>
       <c r="C68">
-        <v>318.3907135749155</v>
+        <v>309.3469622253749</v>
       </c>
       <c r="D68">
-        <v>418.7207135749155</v>
+        <v>418.8319622253749</v>
       </c>
       <c r="E68">
-        <v>589.03</v>
+        <v>598.1849999999999</v>
       </c>
       <c r="F68">
-        <v>604.23</v>
+        <v>613.385</v>
       </c>
       <c r="G68">
         <v>503.9</v>
@@ -7119,28 +7119,28 @@
         <v>243.8</v>
       </c>
       <c r="M68">
-        <v>32.809689</v>
+        <v>33.3068055</v>
       </c>
       <c r="N68">
-        <v>210.990311</v>
+        <v>210.4931945</v>
       </c>
       <c r="O68">
-        <v>34.81340131500001</v>
+        <v>34.7313770925</v>
       </c>
       <c r="P68">
-        <v>176.176909685</v>
+        <v>175.7618174075</v>
       </c>
       <c r="Q68">
-        <v>280.376909685</v>
+        <v>279.9618174075</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1340396532702389</v>
+        <v>0.136545242565072</v>
       </c>
       <c r="T68">
-        <v>1.719955082617219</v>
+        <v>1.768793681624418</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.430731818274779</v>
+        <v>7.319825373225902</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7165,22 +7165,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07543806504647375</v>
+        <v>0.07537791798106627</v>
       </c>
       <c r="C69">
-        <v>309.3469622253749</v>
+        <v>300.303270006185</v>
       </c>
       <c r="D69">
-        <v>418.8319622253749</v>
+        <v>418.9432700061851</v>
       </c>
       <c r="E69">
-        <v>598.1849999999999</v>
+        <v>607.34</v>
       </c>
       <c r="F69">
-        <v>613.385</v>
+        <v>622.5400000000001</v>
       </c>
       <c r="G69">
         <v>503.9</v>
@@ -7201,28 +7201,28 @@
         <v>243.8</v>
       </c>
       <c r="M69">
-        <v>33.3068055</v>
+        <v>33.80392200000001</v>
       </c>
       <c r="N69">
-        <v>210.4931945</v>
+        <v>209.996078</v>
       </c>
       <c r="O69">
-        <v>34.7313770925</v>
+        <v>34.64935287</v>
       </c>
       <c r="P69">
-        <v>175.7618174075</v>
+        <v>175.34672513</v>
       </c>
       <c r="Q69">
-        <v>279.9618174075</v>
+        <v>279.54672513</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.136545242565072</v>
+        <v>0.1392074311908321</v>
       </c>
       <c r="T69">
-        <v>1.768793681624418</v>
+        <v>1.820684693069566</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.319825373225902</v>
+        <v>7.212180882443167</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7247,22 +7247,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07537791798106627</v>
+        <v>0.0753177709156588</v>
       </c>
       <c r="C70">
-        <v>300.303270006185</v>
+        <v>291.2596369645015</v>
       </c>
       <c r="D70">
-        <v>418.9432700061851</v>
+        <v>419.0546369645015</v>
       </c>
       <c r="E70">
-        <v>607.34</v>
+        <v>616.495</v>
       </c>
       <c r="F70">
-        <v>622.5400000000001</v>
+        <v>631.6950000000001</v>
       </c>
       <c r="G70">
         <v>503.9</v>
@@ -7283,28 +7283,28 @@
         <v>243.8</v>
       </c>
       <c r="M70">
-        <v>33.80392200000001</v>
+        <v>34.3010385</v>
       </c>
       <c r="N70">
-        <v>209.996078</v>
+        <v>209.4989615</v>
       </c>
       <c r="O70">
-        <v>34.64935287</v>
+        <v>34.56732864750001</v>
       </c>
       <c r="P70">
-        <v>175.34672513</v>
+        <v>174.9316328525</v>
       </c>
       <c r="Q70">
-        <v>279.54672513</v>
+        <v>279.1316328525</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1392074311908321</v>
+        <v>0.14204137392148</v>
       </c>
       <c r="T70">
-        <v>1.820684693069566</v>
+        <v>1.875923511704724</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.212180882443167</v>
+        <v>7.107656521828049</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7329,22 +7329,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0753177709156588</v>
+        <v>0.07525762385025131</v>
       </c>
       <c r="C71">
-        <v>291.2596369645015</v>
+        <v>282.2160631475298</v>
       </c>
       <c r="D71">
-        <v>419.0546369645015</v>
+        <v>419.1660631475299</v>
       </c>
       <c r="E71">
-        <v>616.495</v>
+        <v>625.65</v>
       </c>
       <c r="F71">
-        <v>631.6950000000001</v>
+        <v>640.85</v>
       </c>
       <c r="G71">
         <v>503.9</v>
@@ -7365,28 +7365,28 @@
         <v>243.8</v>
       </c>
       <c r="M71">
-        <v>34.3010385</v>
+        <v>34.798155</v>
       </c>
       <c r="N71">
-        <v>209.4989615</v>
+        <v>209.001845</v>
       </c>
       <c r="O71">
-        <v>34.56732864750001</v>
+        <v>34.485304425</v>
       </c>
       <c r="P71">
-        <v>174.9316328525</v>
+        <v>174.516540575</v>
       </c>
       <c r="Q71">
-        <v>279.1316328525</v>
+        <v>278.716540575</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.14204137392148</v>
+        <v>0.1450642461675044</v>
       </c>
       <c r="T71">
-        <v>1.875923511704724</v>
+        <v>1.934844918248892</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.107656521828049</v>
+        <v>7.00611857151622</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7411,22 +7411,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07525762385025131</v>
+        <v>0.07519747678484384</v>
       </c>
       <c r="C72">
-        <v>282.2160631475298</v>
+        <v>273.1725486025259</v>
       </c>
       <c r="D72">
-        <v>419.1660631475299</v>
+        <v>419.277548602526</v>
       </c>
       <c r="E72">
-        <v>625.65</v>
+        <v>634.8050000000001</v>
       </c>
       <c r="F72">
-        <v>640.85</v>
+        <v>650.0050000000001</v>
       </c>
       <c r="G72">
         <v>503.9</v>
@@ -7447,28 +7447,28 @@
         <v>243.8</v>
       </c>
       <c r="M72">
-        <v>34.798155</v>
+        <v>35.29527150000001</v>
       </c>
       <c r="N72">
-        <v>209.001845</v>
+        <v>208.5047285</v>
       </c>
       <c r="O72">
-        <v>34.485304425</v>
+        <v>34.4032802025</v>
       </c>
       <c r="P72">
-        <v>174.516540575</v>
+        <v>174.1014482975</v>
       </c>
       <c r="Q72">
-        <v>278.716540575</v>
+        <v>278.3014482975</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1450642461675044</v>
+        <v>0.1482955923615305</v>
       </c>
       <c r="T72">
-        <v>1.934844918248892</v>
+        <v>1.997829870071969</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>7.00611857151622</v>
+        <v>6.907440845156835</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7493,22 +7493,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07519747678484384</v>
+        <v>0.07513732971943636</v>
       </c>
       <c r="C73">
-        <v>273.172548602526</v>
+        <v>264.1290933767963</v>
       </c>
       <c r="D73">
-        <v>419.277548602526</v>
+        <v>419.3890933767963</v>
       </c>
       <c r="E73">
-        <v>634.8049999999999</v>
+        <v>643.9599999999999</v>
       </c>
       <c r="F73">
-        <v>650.005</v>
+        <v>659.16</v>
       </c>
       <c r="G73">
         <v>503.9</v>
@@ -7529,28 +7529,28 @@
         <v>243.8</v>
       </c>
       <c r="M73">
-        <v>35.2952715</v>
+        <v>35.792388</v>
       </c>
       <c r="N73">
-        <v>208.5047285</v>
+        <v>208.007612</v>
       </c>
       <c r="O73">
-        <v>34.4032802025</v>
+        <v>34.32125598</v>
       </c>
       <c r="P73">
-        <v>174.1014482975</v>
+        <v>173.68635602</v>
       </c>
       <c r="Q73">
-        <v>278.3014482975</v>
+        <v>277.88635602</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1482955923615305</v>
+        <v>0.151757748997987</v>
       </c>
       <c r="T73">
-        <v>1.997829870071968</v>
+        <v>2.065313747025264</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.907440845156836</v>
+        <v>6.811504166751882</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7575,22 +7575,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07513732971943636</v>
+        <v>0.07507718265402888</v>
       </c>
       <c r="C74">
-        <v>264.1290933767963</v>
+        <v>255.0856975176973</v>
       </c>
       <c r="D74">
-        <v>419.3890933767963</v>
+        <v>419.5006975176973</v>
       </c>
       <c r="E74">
-        <v>643.9599999999999</v>
+        <v>653.1149999999999</v>
       </c>
       <c r="F74">
-        <v>659.16</v>
+        <v>668.3149999999999</v>
       </c>
       <c r="G74">
         <v>503.9</v>
@@ -7611,28 +7611,28 @@
         <v>243.8</v>
       </c>
       <c r="M74">
-        <v>35.792388</v>
+        <v>36.2895045</v>
       </c>
       <c r="N74">
-        <v>208.007612</v>
+        <v>207.5104955</v>
       </c>
       <c r="O74">
-        <v>34.32125598</v>
+        <v>34.23923175750001</v>
       </c>
       <c r="P74">
-        <v>173.68635602</v>
+        <v>173.2712637425</v>
       </c>
       <c r="Q74">
-        <v>277.88635602</v>
+        <v>277.4712637425</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.151757748997987</v>
+        <v>0.1554763616815885</v>
       </c>
       <c r="T74">
-        <v>2.065313747025264</v>
+        <v>2.137796429678805</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.811504166751882</v>
+        <v>6.718195890495005</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7657,22 +7657,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07507718265402888</v>
+        <v>0.07501703558862141</v>
       </c>
       <c r="C75">
-        <v>255.0856975176973</v>
+        <v>246.0423610726359</v>
       </c>
       <c r="D75">
-        <v>419.5006975176973</v>
+        <v>419.6123610726359</v>
       </c>
       <c r="E75">
-        <v>653.1149999999999</v>
+        <v>662.27</v>
       </c>
       <c r="F75">
-        <v>668.3149999999999</v>
+        <v>677.47</v>
       </c>
       <c r="G75">
         <v>503.9</v>
@@ -7693,28 +7693,28 @@
         <v>243.8</v>
       </c>
       <c r="M75">
-        <v>36.2895045</v>
+        <v>36.786621</v>
       </c>
       <c r="N75">
-        <v>207.5104955</v>
+        <v>207.013379</v>
       </c>
       <c r="O75">
-        <v>34.23923175750001</v>
+        <v>34.157207535</v>
       </c>
       <c r="P75">
-        <v>173.2712637425</v>
+        <v>172.856171465</v>
       </c>
       <c r="Q75">
-        <v>277.4712637425</v>
+        <v>277.056171465</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1554763616815885</v>
+        <v>0.1594810214946977</v>
       </c>
       <c r="T75">
-        <v>2.137796429678805</v>
+        <v>2.215854703305695</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.718195890495005</v>
+        <v>6.62740945954237</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7739,22 +7739,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07501703558862141</v>
+        <v>0.07495688852321392</v>
       </c>
       <c r="C76">
-        <v>246.0423610726359</v>
+        <v>236.9990840890696</v>
       </c>
       <c r="D76">
-        <v>419.6123610726359</v>
+        <v>419.7240840890697</v>
       </c>
       <c r="E76">
-        <v>662.27</v>
+        <v>671.425</v>
       </c>
       <c r="F76">
-        <v>677.47</v>
+        <v>686.625</v>
       </c>
       <c r="G76">
         <v>503.9</v>
@@ -7775,28 +7775,28 @@
         <v>243.8</v>
       </c>
       <c r="M76">
-        <v>36.786621</v>
+        <v>37.2837375</v>
       </c>
       <c r="N76">
-        <v>207.013379</v>
+        <v>206.5162625</v>
       </c>
       <c r="O76">
-        <v>34.157207535</v>
+        <v>34.0751833125</v>
       </c>
       <c r="P76">
-        <v>172.856171465</v>
+        <v>172.4410791875</v>
       </c>
       <c r="Q76">
-        <v>277.056171465</v>
+        <v>276.6410791875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1594810214946977</v>
+        <v>0.1638060540928557</v>
       </c>
       <c r="T76">
-        <v>2.215854703305695</v>
+        <v>2.300157638822736</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.62740945954237</v>
+        <v>6.539044000081805</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7821,22 +7821,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07495688852321392</v>
+        <v>0.07489674145780645</v>
       </c>
       <c r="C77">
-        <v>236.9990840890696</v>
+        <v>227.9558666145066</v>
       </c>
       <c r="D77">
-        <v>419.7240840890697</v>
+        <v>419.8358666145066</v>
       </c>
       <c r="E77">
-        <v>671.425</v>
+        <v>680.5799999999999</v>
       </c>
       <c r="F77">
-        <v>686.625</v>
+        <v>695.78</v>
       </c>
       <c r="G77">
         <v>503.9</v>
@@ -7857,28 +7857,28 @@
         <v>243.8</v>
       </c>
       <c r="M77">
-        <v>37.2837375</v>
+        <v>37.780854</v>
       </c>
       <c r="N77">
-        <v>206.5162625</v>
+        <v>206.019146</v>
       </c>
       <c r="O77">
-        <v>34.0751833125</v>
+        <v>33.99315909000001</v>
       </c>
       <c r="P77">
-        <v>172.4410791875</v>
+        <v>172.02598691</v>
       </c>
       <c r="Q77">
-        <v>276.6410791875</v>
+        <v>276.22598691</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1638060540928557</v>
+        <v>0.1684915060741936</v>
       </c>
       <c r="T77">
-        <v>2.300157638822736</v>
+        <v>2.391485818966197</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.539044000081805</v>
+        <v>6.45300394744915</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7903,22 +7903,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07489674145780645</v>
+        <v>0.07483659439239897</v>
       </c>
       <c r="C78">
-        <v>227.9558666145066</v>
+        <v>218.9127086965053</v>
       </c>
       <c r="D78">
-        <v>419.8358666145066</v>
+        <v>419.9477086965053</v>
       </c>
       <c r="E78">
-        <v>680.5799999999999</v>
+        <v>689.735</v>
       </c>
       <c r="F78">
-        <v>695.78</v>
+        <v>704.9350000000001</v>
       </c>
       <c r="G78">
         <v>503.9</v>
@@ -7939,28 +7939,28 @@
         <v>243.8</v>
       </c>
       <c r="M78">
-        <v>37.780854</v>
+        <v>38.2779705</v>
       </c>
       <c r="N78">
-        <v>206.019146</v>
+        <v>205.5220295</v>
       </c>
       <c r="O78">
-        <v>33.99315909000001</v>
+        <v>33.9111348675</v>
       </c>
       <c r="P78">
-        <v>172.02598691</v>
+        <v>171.6108946325</v>
       </c>
       <c r="Q78">
-        <v>276.22598691</v>
+        <v>275.8108946325</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1684915060741936</v>
+        <v>0.1735843886626042</v>
       </c>
       <c r="T78">
-        <v>2.391485818966197</v>
+        <v>2.490755579991698</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.45300394744915</v>
+        <v>6.369198701378381</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7985,22 +7985,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07483659439239897</v>
+        <v>0.07477644732699149</v>
       </c>
       <c r="C79">
-        <v>218.9127086965053</v>
+        <v>209.8696103826752</v>
       </c>
       <c r="D79">
-        <v>419.9477086965053</v>
+        <v>420.0596103826753</v>
       </c>
       <c r="E79">
-        <v>689.735</v>
+        <v>698.89</v>
       </c>
       <c r="F79">
-        <v>704.9350000000001</v>
+        <v>714.09</v>
       </c>
       <c r="G79">
         <v>503.9</v>
@@ -8021,28 +8021,28 @@
         <v>243.8</v>
       </c>
       <c r="M79">
-        <v>38.2779705</v>
+        <v>38.775087</v>
       </c>
       <c r="N79">
-        <v>205.5220295</v>
+        <v>205.024913</v>
       </c>
       <c r="O79">
-        <v>33.9111348675</v>
+        <v>33.82911064500001</v>
       </c>
       <c r="P79">
-        <v>171.6108946325</v>
+        <v>171.195802355</v>
       </c>
       <c r="Q79">
-        <v>275.8108946325</v>
+        <v>275.395802355</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1735843886626042</v>
+        <v>0.1791402605772341</v>
       </c>
       <c r="T79">
-        <v>2.490755579991698</v>
+        <v>2.59904986474679</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.369198701378381</v>
+        <v>6.287542307770967</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8067,22 +8067,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07477644732699149</v>
+        <v>0.07471630026158402</v>
       </c>
       <c r="C80">
-        <v>209.8696103826752</v>
+        <v>200.8265717206765</v>
       </c>
       <c r="D80">
-        <v>420.0596103826753</v>
+        <v>420.1715717206766</v>
       </c>
       <c r="E80">
-        <v>698.89</v>
+        <v>708.045</v>
       </c>
       <c r="F80">
-        <v>714.09</v>
+        <v>723.245</v>
       </c>
       <c r="G80">
         <v>503.9</v>
@@ -8103,28 +8103,28 @@
         <v>243.8</v>
       </c>
       <c r="M80">
-        <v>38.775087</v>
+        <v>39.2722035</v>
       </c>
       <c r="N80">
-        <v>205.024913</v>
+        <v>204.5277965</v>
       </c>
       <c r="O80">
-        <v>33.82911064500001</v>
+        <v>33.7470864225</v>
       </c>
       <c r="P80">
-        <v>171.195802355</v>
+        <v>170.7807100775</v>
       </c>
       <c r="Q80">
-        <v>275.395802355</v>
+        <v>274.9807100775</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1791402605772341</v>
+        <v>0.1852252631504001</v>
       </c>
       <c r="T80">
-        <v>2.59904986474679</v>
+        <v>2.71765789090713</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.287542307770967</v>
+        <v>6.207953164634625</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8149,22 +8149,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07471630026158402</v>
+        <v>0.07465615319617654</v>
       </c>
       <c r="C81">
-        <v>200.8265717206765</v>
+        <v>191.78359275822</v>
       </c>
       <c r="D81">
-        <v>420.1715717206766</v>
+        <v>420.2835927582201</v>
       </c>
       <c r="E81">
-        <v>708.045</v>
+        <v>717.2</v>
       </c>
       <c r="F81">
-        <v>723.245</v>
+        <v>732.4000000000001</v>
       </c>
       <c r="G81">
         <v>503.9</v>
@@ -8185,28 +8185,28 @@
         <v>243.8</v>
       </c>
       <c r="M81">
-        <v>39.2722035</v>
+        <v>39.76932000000001</v>
       </c>
       <c r="N81">
-        <v>204.5277965</v>
+        <v>204.03068</v>
       </c>
       <c r="O81">
-        <v>33.7470864225</v>
+        <v>33.6650622</v>
       </c>
       <c r="P81">
-        <v>170.7807100775</v>
+        <v>170.3656178</v>
       </c>
       <c r="Q81">
-        <v>274.9807100775</v>
+        <v>274.5656178</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1852252631504001</v>
+        <v>0.1919187659808827</v>
       </c>
       <c r="T81">
-        <v>2.71765789090713</v>
+        <v>2.848126719683502</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.207953164634625</v>
+        <v>6.130353750076692</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8231,22 +8231,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07465615319617654</v>
+        <v>0.07527235613076907</v>
       </c>
       <c r="C82">
-        <v>191.78359275822</v>
+        <v>181.4837652015764</v>
       </c>
       <c r="D82">
-        <v>420.2835927582201</v>
+        <v>419.1387652015765</v>
       </c>
       <c r="E82">
-        <v>717.2</v>
+        <v>726.355</v>
       </c>
       <c r="F82">
-        <v>732.4000000000001</v>
+        <v>741.5550000000001</v>
       </c>
       <c r="G82">
         <v>503.9</v>
@@ -8267,45 +8267,45 @@
         <v>243.8</v>
       </c>
       <c r="M82">
-        <v>39.76932000000001</v>
+        <v>41.0079915</v>
       </c>
       <c r="N82">
-        <v>204.03068</v>
+        <v>202.7920085</v>
       </c>
       <c r="O82">
-        <v>33.6650622</v>
+        <v>33.4606814025</v>
       </c>
       <c r="P82">
-        <v>170.3656178</v>
+        <v>169.3313270975</v>
       </c>
       <c r="Q82">
-        <v>274.5656178</v>
+        <v>273.5313270975</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1919187659808827</v>
+        <v>0.1993168480566793</v>
       </c>
       <c r="T82">
-        <v>2.848126719683502</v>
+        <v>2.992329109383705</v>
       </c>
       <c r="U82">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V82">
         <v>0.165</v>
       </c>
       <c r="W82">
-        <v>0.0453405</v>
+        <v>0.0461755</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>6.130353750076692</v>
+        <v>5.945182660311466</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8313,22 +8313,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07527235613076907</v>
+        <v>0.07522055906536157</v>
       </c>
       <c r="C83">
-        <v>181.4837652015764</v>
+        <v>172.4247574828636</v>
       </c>
       <c r="D83">
-        <v>419.1387652015765</v>
+        <v>419.2347574828636</v>
       </c>
       <c r="E83">
-        <v>726.355</v>
+        <v>735.51</v>
       </c>
       <c r="F83">
-        <v>741.5550000000001</v>
+        <v>750.71</v>
       </c>
       <c r="G83">
         <v>503.9</v>
@@ -8349,28 +8349,28 @@
         <v>243.8</v>
       </c>
       <c r="M83">
-        <v>41.0079915</v>
+        <v>41.51426300000001</v>
       </c>
       <c r="N83">
-        <v>202.7920085</v>
+        <v>202.285737</v>
       </c>
       <c r="O83">
-        <v>33.4606814025</v>
+        <v>33.377146605</v>
       </c>
       <c r="P83">
-        <v>169.3313270975</v>
+        <v>168.908590395</v>
       </c>
       <c r="Q83">
-        <v>273.5313270975</v>
+        <v>273.108590395</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1993168480566793</v>
+        <v>0.2075369392520088</v>
       </c>
       <c r="T83">
-        <v>2.992329109383705</v>
+        <v>3.152553986828373</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.945182660311466</v>
+        <v>5.872680432746692</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8395,22 +8395,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07522055906536157</v>
+        <v>0.07516876199995409</v>
       </c>
       <c r="C84">
-        <v>172.4247574828636</v>
+        <v>163.3657937430412</v>
       </c>
       <c r="D84">
-        <v>419.2347574828636</v>
+        <v>419.3307937430412</v>
       </c>
       <c r="E84">
-        <v>735.51</v>
+        <v>744.665</v>
       </c>
       <c r="F84">
-        <v>750.71</v>
+        <v>759.865</v>
       </c>
       <c r="G84">
         <v>503.9</v>
@@ -8431,28 +8431,28 @@
         <v>243.8</v>
       </c>
       <c r="M84">
-        <v>41.51426300000001</v>
+        <v>42.0205345</v>
       </c>
       <c r="N84">
-        <v>202.285737</v>
+        <v>201.7794655</v>
       </c>
       <c r="O84">
-        <v>33.377146605</v>
+        <v>33.29361180750001</v>
       </c>
       <c r="P84">
-        <v>168.908590395</v>
+        <v>168.4858536925</v>
       </c>
       <c r="Q84">
-        <v>273.108590395</v>
+        <v>272.6858536925</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2075369392520088</v>
+        <v>0.2167240999997301</v>
       </c>
       <c r="T84">
-        <v>3.152553986828373</v>
+        <v>3.331628849854767</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.872680432746692</v>
+        <v>5.801925246809986</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8477,22 +8477,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07516876199995409</v>
+        <v>0.07511696493454662</v>
       </c>
       <c r="C85">
-        <v>163.3657937430412</v>
+        <v>154.3068740123392</v>
       </c>
       <c r="D85">
-        <v>419.3307937430412</v>
+        <v>419.4268740123393</v>
       </c>
       <c r="E85">
-        <v>744.665</v>
+        <v>753.8200000000001</v>
       </c>
       <c r="F85">
-        <v>759.865</v>
+        <v>769.0200000000001</v>
       </c>
       <c r="G85">
         <v>503.9</v>
@@ -8513,28 +8513,28 @@
         <v>243.8</v>
       </c>
       <c r="M85">
-        <v>42.0205345</v>
+        <v>42.52680600000001</v>
       </c>
       <c r="N85">
-        <v>201.7794655</v>
+        <v>201.273194</v>
       </c>
       <c r="O85">
-        <v>33.29361180750001</v>
+        <v>33.21007701</v>
       </c>
       <c r="P85">
-        <v>168.4858536925</v>
+        <v>168.06311699</v>
       </c>
       <c r="Q85">
-        <v>272.6858536925</v>
+        <v>272.26311699</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2167240999997301</v>
+        <v>0.2270596558409165</v>
       </c>
       <c r="T85">
-        <v>3.331628849854767</v>
+        <v>3.533088070759461</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.801925246809986</v>
+        <v>5.732854708157484</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8559,22 +8559,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07511696493454663</v>
+        <v>0.07506516786913914</v>
       </c>
       <c r="C86">
-        <v>154.3068740123393</v>
+        <v>145.2479983210162</v>
       </c>
       <c r="D86">
-        <v>419.4268740123393</v>
+        <v>419.5229983210162</v>
       </c>
       <c r="E86">
-        <v>753.8199999999999</v>
+        <v>762.9749999999999</v>
       </c>
       <c r="F86">
-        <v>769.02</v>
+        <v>778.175</v>
       </c>
       <c r="G86">
         <v>503.9</v>
@@ -8595,28 +8595,28 @@
         <v>243.8</v>
       </c>
       <c r="M86">
-        <v>42.526806</v>
+        <v>43.0330775</v>
       </c>
       <c r="N86">
-        <v>201.273194</v>
+        <v>200.7669225</v>
       </c>
       <c r="O86">
-        <v>33.21007701000001</v>
+        <v>33.12654221250001</v>
       </c>
       <c r="P86">
-        <v>168.06311699</v>
+        <v>167.6403802875</v>
       </c>
       <c r="Q86">
-        <v>272.26311699</v>
+        <v>271.8403802875</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2270596558409164</v>
+        <v>0.2387732857942609</v>
       </c>
       <c r="T86">
-        <v>3.533088070759459</v>
+        <v>3.761408521118111</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.732854708157486</v>
+        <v>5.665409358649751</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8641,22 +8641,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07506516786913914</v>
+        <v>0.07501337080373166</v>
       </c>
       <c r="C87">
-        <v>145.2479983210162</v>
+        <v>136.1891666993573</v>
       </c>
       <c r="D87">
-        <v>419.5229983210162</v>
+        <v>419.6191666993574</v>
       </c>
       <c r="E87">
-        <v>762.9749999999999</v>
+        <v>772.13</v>
       </c>
       <c r="F87">
-        <v>778.175</v>
+        <v>787.33</v>
       </c>
       <c r="G87">
         <v>503.9</v>
@@ -8677,28 +8677,28 @@
         <v>243.8</v>
       </c>
       <c r="M87">
-        <v>43.0330775</v>
+        <v>43.539349</v>
       </c>
       <c r="N87">
-        <v>200.7669225</v>
+        <v>200.260651</v>
       </c>
       <c r="O87">
-        <v>33.12654221250001</v>
+        <v>33.043007415</v>
       </c>
       <c r="P87">
-        <v>167.6403802875</v>
+        <v>167.217643585</v>
       </c>
       <c r="Q87">
-        <v>271.8403802875</v>
+        <v>271.417643585</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2387732857942609</v>
+        <v>0.2521602914552262</v>
       </c>
       <c r="T87">
-        <v>3.761408521118111</v>
+        <v>4.022346178670857</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.665409358649751</v>
+        <v>5.599532505642195</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8723,22 +8723,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07501337080373166</v>
+        <v>0.07496157373832418</v>
       </c>
       <c r="C88">
-        <v>136.1891666993573</v>
+        <v>127.1303791776767</v>
       </c>
       <c r="D88">
-        <v>419.6191666993574</v>
+        <v>419.7153791776767</v>
       </c>
       <c r="E88">
-        <v>772.13</v>
+        <v>781.285</v>
       </c>
       <c r="F88">
-        <v>787.33</v>
+        <v>796.485</v>
       </c>
       <c r="G88">
         <v>503.9</v>
@@ -8759,28 +8759,28 @@
         <v>243.8</v>
       </c>
       <c r="M88">
-        <v>43.539349</v>
+        <v>44.04562050000001</v>
       </c>
       <c r="N88">
-        <v>200.260651</v>
+        <v>199.7543795</v>
       </c>
       <c r="O88">
-        <v>33.043007415</v>
+        <v>32.9594726175</v>
       </c>
       <c r="P88">
-        <v>167.217643585</v>
+        <v>166.7949068825</v>
       </c>
       <c r="Q88">
-        <v>271.417643585</v>
+        <v>270.9949068825</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2521602914552262</v>
+        <v>0.2676068364486475</v>
       </c>
       <c r="T88">
-        <v>4.022346178670857</v>
+        <v>4.323428091231717</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.599532505642195</v>
+        <v>5.535170063048606</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8805,22 +8805,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07496157373832418</v>
+        <v>0.07490977667291671</v>
       </c>
       <c r="C89">
-        <v>127.1303791776767</v>
+        <v>118.0716357863154</v>
       </c>
       <c r="D89">
-        <v>419.7153791776767</v>
+        <v>419.8116357863153</v>
       </c>
       <c r="E89">
-        <v>781.285</v>
+        <v>790.4399999999999</v>
       </c>
       <c r="F89">
-        <v>796.485</v>
+        <v>805.64</v>
       </c>
       <c r="G89">
         <v>503.9</v>
@@ -8841,28 +8841,28 @@
         <v>243.8</v>
       </c>
       <c r="M89">
-        <v>44.04562050000001</v>
+        <v>44.551892</v>
       </c>
       <c r="N89">
-        <v>199.7543795</v>
+        <v>199.248108</v>
       </c>
       <c r="O89">
-        <v>32.9594726175</v>
+        <v>32.87593782</v>
       </c>
       <c r="P89">
-        <v>166.7949068825</v>
+        <v>166.37217018</v>
       </c>
       <c r="Q89">
-        <v>270.9949068825</v>
+        <v>270.57217018</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2676068364486475</v>
+        <v>0.2856278056076393</v>
       </c>
       <c r="T89">
-        <v>4.323428091231717</v>
+        <v>4.674690322552722</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.535170063048606</v>
+        <v>5.472270403241236</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8887,22 +8887,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07490977667291671</v>
+        <v>0.07485797960750923</v>
       </c>
       <c r="C90">
-        <v>118.0716357863154</v>
+        <v>109.0129365556427</v>
       </c>
       <c r="D90">
-        <v>419.8116357863153</v>
+        <v>419.9079365556427</v>
       </c>
       <c r="E90">
-        <v>790.4399999999999</v>
+        <v>799.5949999999999</v>
       </c>
       <c r="F90">
-        <v>805.64</v>
+        <v>814.795</v>
       </c>
       <c r="G90">
         <v>503.9</v>
@@ -8923,28 +8923,28 @@
         <v>243.8</v>
       </c>
       <c r="M90">
-        <v>44.551892</v>
+        <v>45.0581635</v>
       </c>
       <c r="N90">
-        <v>199.248108</v>
+        <v>198.7418365</v>
       </c>
       <c r="O90">
-        <v>32.87593782</v>
+        <v>32.7924030225</v>
       </c>
       <c r="P90">
-        <v>166.37217018</v>
+        <v>165.9494334775</v>
       </c>
       <c r="Q90">
-        <v>270.57217018</v>
+        <v>270.1494334775</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2856278056076393</v>
+        <v>0.3069253146137202</v>
       </c>
       <c r="T90">
-        <v>4.674690322552722</v>
+        <v>5.089818414113908</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.472270403241236</v>
+        <v>5.410784218935155</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8969,22 +8969,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07485797960750923</v>
+        <v>0.07480618254210175</v>
       </c>
       <c r="C91">
-        <v>109.0129365556427</v>
+        <v>99.95428151605563</v>
       </c>
       <c r="D91">
-        <v>419.9079365556427</v>
+        <v>420.0042815160557</v>
       </c>
       <c r="E91">
-        <v>799.5949999999999</v>
+        <v>808.75</v>
       </c>
       <c r="F91">
-        <v>814.795</v>
+        <v>823.95</v>
       </c>
       <c r="G91">
         <v>503.9</v>
@@ -9005,28 +9005,28 @@
         <v>243.8</v>
       </c>
       <c r="M91">
-        <v>45.0581635</v>
+        <v>45.564435</v>
       </c>
       <c r="N91">
-        <v>198.7418365</v>
+        <v>198.235565</v>
       </c>
       <c r="O91">
-        <v>32.7924030225</v>
+        <v>32.708868225</v>
       </c>
       <c r="P91">
-        <v>165.9494334775</v>
+        <v>165.526696775</v>
       </c>
       <c r="Q91">
-        <v>270.1494334775</v>
+        <v>269.726696775</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3069253146137202</v>
+        <v>0.3324823254210176</v>
       </c>
       <c r="T91">
-        <v>5.089818414113908</v>
+        <v>5.587972123987332</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.410784218935155</v>
+        <v>5.35066439428032</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9051,22 +9051,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07480618254210175</v>
+        <v>0.07475438547669427</v>
       </c>
       <c r="C92">
-        <v>99.95428151605563</v>
+        <v>90.89567069797931</v>
       </c>
       <c r="D92">
-        <v>420.0042815160557</v>
+        <v>420.1006706979794</v>
       </c>
       <c r="E92">
-        <v>808.75</v>
+        <v>817.905</v>
       </c>
       <c r="F92">
-        <v>823.95</v>
+        <v>833.105</v>
       </c>
       <c r="G92">
         <v>503.9</v>
@@ -9087,28 +9087,28 @@
         <v>243.8</v>
       </c>
       <c r="M92">
-        <v>45.564435</v>
+        <v>46.0707065</v>
       </c>
       <c r="N92">
-        <v>198.235565</v>
+        <v>197.7292935</v>
       </c>
       <c r="O92">
-        <v>32.708868225</v>
+        <v>32.6253334275</v>
       </c>
       <c r="P92">
-        <v>165.526696775</v>
+        <v>165.1039600725</v>
       </c>
       <c r="Q92">
-        <v>269.726696775</v>
+        <v>269.3039600725</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3324823254210176</v>
+        <v>0.3637186719632698</v>
       </c>
       <c r="T92">
-        <v>5.587972123987332</v>
+        <v>6.196826658277073</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.35066439428032</v>
+        <v>5.291865884453063</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9133,22 +9133,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07475438547669427</v>
+        <v>0.0747025884112868</v>
       </c>
       <c r="C93">
-        <v>90.89567069797931</v>
+        <v>81.83710413186679</v>
       </c>
       <c r="D93">
-        <v>420.1006706979794</v>
+        <v>420.1971041318668</v>
       </c>
       <c r="E93">
-        <v>817.905</v>
+        <v>827.0599999999999</v>
       </c>
       <c r="F93">
-        <v>833.105</v>
+        <v>842.26</v>
       </c>
       <c r="G93">
         <v>503.9</v>
@@ -9169,28 +9169,28 @@
         <v>243.8</v>
       </c>
       <c r="M93">
-        <v>46.0707065</v>
+        <v>46.576978</v>
       </c>
       <c r="N93">
-        <v>197.7292935</v>
+        <v>197.223022</v>
       </c>
       <c r="O93">
-        <v>32.6253334275</v>
+        <v>32.54179863</v>
       </c>
       <c r="P93">
-        <v>165.1039600725</v>
+        <v>164.68122337</v>
       </c>
       <c r="Q93">
-        <v>269.3039600725</v>
+        <v>268.88122337</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3637186719632698</v>
+        <v>0.4027641051410852</v>
       </c>
       <c r="T93">
-        <v>6.196826658277073</v>
+        <v>6.957894826139251</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.291865884453063</v>
+        <v>5.234345603100313</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9215,22 +9215,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0747025884112868</v>
+        <v>0.07465079134587932</v>
       </c>
       <c r="C94">
-        <v>81.83710413186679</v>
+        <v>72.77858184819866</v>
       </c>
       <c r="D94">
-        <v>420.1971041318668</v>
+        <v>420.2935818481988</v>
       </c>
       <c r="E94">
-        <v>827.0599999999999</v>
+        <v>836.215</v>
       </c>
       <c r="F94">
-        <v>842.26</v>
+        <v>851.4150000000001</v>
       </c>
       <c r="G94">
         <v>503.9</v>
@@ -9251,28 +9251,28 @@
         <v>243.8</v>
       </c>
       <c r="M94">
-        <v>46.576978</v>
+        <v>47.08324950000001</v>
       </c>
       <c r="N94">
-        <v>197.223022</v>
+        <v>196.7167505</v>
       </c>
       <c r="O94">
-        <v>32.54179863</v>
+        <v>32.4582638325</v>
       </c>
       <c r="P94">
-        <v>164.68122337</v>
+        <v>164.2584866675</v>
       </c>
       <c r="Q94">
-        <v>268.88122337</v>
+        <v>268.4584866675</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4027641051410852</v>
+        <v>0.4529653763697048</v>
       </c>
       <c r="T94">
-        <v>6.957894826139251</v>
+        <v>7.936411041962048</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.234345603100313</v>
+        <v>5.17806231704547</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9297,22 +9297,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07465079134587932</v>
+        <v>0.07459899428047183</v>
       </c>
       <c r="C95">
-        <v>72.77858184819866</v>
+        <v>63.72010387748412</v>
       </c>
       <c r="D95">
-        <v>420.2935818481988</v>
+        <v>420.3901038774841</v>
       </c>
       <c r="E95">
-        <v>836.215</v>
+        <v>845.37</v>
       </c>
       <c r="F95">
-        <v>851.4150000000001</v>
+        <v>860.5700000000001</v>
       </c>
       <c r="G95">
         <v>503.9</v>
@@ -9333,28 +9333,28 @@
         <v>243.8</v>
       </c>
       <c r="M95">
-        <v>47.08324950000001</v>
+        <v>47.589521</v>
       </c>
       <c r="N95">
-        <v>196.7167505</v>
+        <v>196.210479</v>
       </c>
       <c r="O95">
-        <v>32.4582638325</v>
+        <v>32.374729035</v>
       </c>
       <c r="P95">
-        <v>164.2584866675</v>
+        <v>163.835749965</v>
       </c>
       <c r="Q95">
-        <v>268.4584866675</v>
+        <v>268.035749965</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4529653763697048</v>
+        <v>0.519900404674531</v>
       </c>
       <c r="T95">
-        <v>7.936411041962048</v>
+        <v>9.241099329725779</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.17806231704547</v>
+        <v>5.1229765477152</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9379,22 +9379,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07459899428047183</v>
+        <v>0.07454719721506436</v>
       </c>
       <c r="C96">
-        <v>63.72010387748412</v>
+        <v>54.66167025025982</v>
       </c>
       <c r="D96">
-        <v>420.3901038774841</v>
+        <v>420.4866702502598</v>
       </c>
       <c r="E96">
-        <v>845.37</v>
+        <v>854.525</v>
       </c>
       <c r="F96">
-        <v>860.5700000000001</v>
+        <v>869.725</v>
       </c>
       <c r="G96">
         <v>503.9</v>
@@ -9415,28 +9415,28 @@
         <v>243.8</v>
       </c>
       <c r="M96">
-        <v>47.589521</v>
+        <v>48.0957925</v>
       </c>
       <c r="N96">
-        <v>196.210479</v>
+        <v>195.7042075</v>
       </c>
       <c r="O96">
-        <v>32.374729035</v>
+        <v>32.2911942375</v>
       </c>
       <c r="P96">
-        <v>163.835749965</v>
+        <v>163.4130132625</v>
       </c>
       <c r="Q96">
-        <v>268.035749965</v>
+        <v>267.6130132625</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.519900404674531</v>
+        <v>0.6136094443012879</v>
       </c>
       <c r="T96">
-        <v>9.241099329725779</v>
+        <v>11.06766293259501</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.1229765477152</v>
+        <v>5.069050478791882</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9461,22 +9461,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07454719721506436</v>
+        <v>0.07449540014965687</v>
       </c>
       <c r="C97">
-        <v>54.66167025025982</v>
+        <v>45.60328099709079</v>
       </c>
       <c r="D97">
-        <v>420.4866702502598</v>
+        <v>420.5832809970909</v>
       </c>
       <c r="E97">
-        <v>854.525</v>
+        <v>863.6800000000001</v>
       </c>
       <c r="F97">
-        <v>869.725</v>
+        <v>878.8800000000001</v>
       </c>
       <c r="G97">
         <v>503.9</v>
@@ -9497,28 +9497,28 @@
         <v>243.8</v>
       </c>
       <c r="M97">
-        <v>48.0957925</v>
+        <v>48.60206400000001</v>
       </c>
       <c r="N97">
-        <v>195.7042075</v>
+        <v>195.197936</v>
       </c>
       <c r="O97">
-        <v>32.2911942375</v>
+        <v>32.20765944</v>
       </c>
       <c r="P97">
-        <v>163.4130132625</v>
+        <v>162.99027656</v>
       </c>
       <c r="Q97">
-        <v>267.6130132625</v>
+        <v>267.19027656</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6136094443012879</v>
+        <v>0.7541730037414233</v>
       </c>
       <c r="T97">
-        <v>11.06766293259501</v>
+        <v>13.80750833689885</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.069050478791882</v>
+        <v>5.016247869637799</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9543,22 +9543,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07449540014965687</v>
+        <v>0.07444360308424941</v>
       </c>
       <c r="C98">
-        <v>45.60328099709091</v>
+        <v>36.5449361485704</v>
       </c>
       <c r="D98">
-        <v>420.5832809970909</v>
+        <v>420.6799361485704</v>
       </c>
       <c r="E98">
-        <v>863.6799999999999</v>
+        <v>872.8349999999999</v>
       </c>
       <c r="F98">
-        <v>878.88</v>
+        <v>888.035</v>
       </c>
       <c r="G98">
         <v>503.9</v>
@@ -9579,28 +9579,28 @@
         <v>243.8</v>
       </c>
       <c r="M98">
-        <v>48.602064</v>
+        <v>49.1083355</v>
       </c>
       <c r="N98">
-        <v>195.197936</v>
+        <v>194.6916645</v>
       </c>
       <c r="O98">
-        <v>32.20765944000001</v>
+        <v>32.1241246425</v>
       </c>
       <c r="P98">
-        <v>162.99027656</v>
+        <v>162.5675398575</v>
       </c>
       <c r="Q98">
-        <v>267.19027656</v>
+        <v>266.7675398575</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7541730037414214</v>
+        <v>0.9884456028083126</v>
       </c>
       <c r="T98">
-        <v>13.80750833689881</v>
+        <v>18.37391734407186</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.016247869637801</v>
+        <v>4.964533974074524</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9625,22 +9625,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07444360308424941</v>
+        <v>0.07439180601884193</v>
       </c>
       <c r="C99">
-        <v>36.5449361485704</v>
+        <v>27.48663573531974</v>
       </c>
       <c r="D99">
-        <v>420.6799361485704</v>
+        <v>420.7766357353197</v>
       </c>
       <c r="E99">
-        <v>872.8349999999999</v>
+        <v>881.9899999999999</v>
       </c>
       <c r="F99">
-        <v>888.035</v>
+        <v>897.1899999999999</v>
       </c>
       <c r="G99">
         <v>503.9</v>
@@ -9661,28 +9661,28 @@
         <v>243.8</v>
       </c>
       <c r="M99">
-        <v>49.1083355</v>
+        <v>49.614607</v>
       </c>
       <c r="N99">
-        <v>194.6916645</v>
+        <v>194.185393</v>
       </c>
       <c r="O99">
-        <v>32.1241246425</v>
+        <v>32.040589845</v>
       </c>
       <c r="P99">
-        <v>162.5675398575</v>
+        <v>162.144803155</v>
       </c>
       <c r="Q99">
-        <v>266.7675398575</v>
+        <v>266.344803155</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9884456028083126</v>
+        <v>1.456990800942095</v>
       </c>
       <c r="T99">
-        <v>18.37391734407186</v>
+        <v>27.50673535841795</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.964533974074524</v>
+        <v>4.913875464134987</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9707,22 +9707,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07439180601884193</v>
+        <v>0.07434000895343444</v>
       </c>
       <c r="C100">
-        <v>27.48663573531974</v>
+        <v>18.42837978798798</v>
       </c>
       <c r="D100">
-        <v>420.7766357353197</v>
+        <v>420.873379787988</v>
       </c>
       <c r="E100">
-        <v>881.9899999999999</v>
+        <v>891.145</v>
       </c>
       <c r="F100">
-        <v>897.1899999999999</v>
+        <v>906.345</v>
       </c>
       <c r="G100">
         <v>503.9</v>
@@ -9743,28 +9743,28 @@
         <v>243.8</v>
       </c>
       <c r="M100">
-        <v>49.614607</v>
+        <v>50.1208785</v>
       </c>
       <c r="N100">
-        <v>194.185393</v>
+        <v>193.6791215</v>
       </c>
       <c r="O100">
-        <v>32.040589845</v>
+        <v>31.9570550475</v>
       </c>
       <c r="P100">
-        <v>162.144803155</v>
+        <v>161.7220664525</v>
       </c>
       <c r="Q100">
-        <v>266.344803155</v>
+        <v>265.9220664525</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.456990800942095</v>
+        <v>2.862626395343442</v>
       </c>
       <c r="T100">
-        <v>27.50673535841795</v>
+        <v>54.90518940145621</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9781,91 +9781,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.913875464134987</v>
+        <v>4.864240358436654</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07434000895343444</v>
-      </c>
-      <c r="C101">
-        <v>18.42837978798798</v>
-      </c>
-      <c r="D101">
-        <v>420.873379787988</v>
-      </c>
-      <c r="E101">
-        <v>891.145</v>
-      </c>
-      <c r="F101">
-        <v>906.345</v>
-      </c>
-      <c r="G101">
-        <v>503.9</v>
-      </c>
-      <c r="H101">
-        <v>900.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>348</v>
-      </c>
-      <c r="K101">
-        <v>104.2</v>
-      </c>
-      <c r="L101">
-        <v>243.8</v>
-      </c>
-      <c r="M101">
-        <v>50.1208785</v>
-      </c>
-      <c r="N101">
-        <v>193.6791215</v>
-      </c>
-      <c r="O101">
-        <v>31.9570550475</v>
-      </c>
-      <c r="P101">
-        <v>161.7220664525</v>
-      </c>
-      <c r="Q101">
-        <v>265.9220664525</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.862626395343442</v>
-      </c>
-      <c r="T101">
-        <v>54.90518940145621</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.165</v>
-      </c>
-      <c r="W101">
-        <v>0.0461755</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.864240358436654</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
